--- a/IgniteDigitalization.Server/Initializers/IGNITE_S1_Digitalizacja.xlsx
+++ b/IgniteDigitalization.Server/Initializers/IGNITE_S1_Digitalizacja.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Decisions" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Feedbacks" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Processes" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Cards" sheetId="4" state="hidden" r:id="rId6"/>
+    <sheet name="Cards" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="CardsWeights" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="CardsEnablers" sheetId="6" state="hidden" r:id="rId8"/>
+    <sheet name="CardsEnablers" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="EconomyRules" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -1061,13 +1061,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF375623"/>
@@ -1092,6 +1085,13 @@
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1271,435 +1271,435 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14357,10 +14357,10 @@
       <c r="I6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0"/>
+      <c r="A7" s="60"/>
     </row>
     <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0"/>
+      <c r="A8" s="60"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23"/>
@@ -14496,3923 +14496,3923 @@
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="25"/>
-      <c r="E21" s="60"/>
+      <c r="E21" s="61"/>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="25"/>
-      <c r="E22" s="60"/>
+      <c r="E22" s="61"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="25"/>
-      <c r="E23" s="60"/>
+      <c r="E23" s="61"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="25"/>
-      <c r="E24" s="60"/>
+      <c r="E24" s="61"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="25"/>
-      <c r="E25" s="60"/>
+      <c r="E25" s="61"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="25"/>
-      <c r="E26" s="60"/>
+      <c r="E26" s="61"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="25"/>
-      <c r="E27" s="60"/>
+      <c r="E27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="25"/>
-      <c r="E28" s="60"/>
+      <c r="E28" s="61"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="25"/>
-      <c r="E29" s="60"/>
+      <c r="E29" s="61"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="25"/>
-      <c r="E30" s="60"/>
+      <c r="E30" s="61"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="25"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="61"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25"/>
-      <c r="E32" s="60"/>
+      <c r="E32" s="61"/>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="25"/>
-      <c r="E33" s="60"/>
+      <c r="E33" s="61"/>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="25"/>
-      <c r="E34" s="60"/>
+      <c r="E34" s="61"/>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="25"/>
-      <c r="E35" s="60"/>
+      <c r="E35" s="61"/>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="25"/>
-      <c r="E36" s="60"/>
+      <c r="E36" s="61"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="25"/>
-      <c r="E37" s="60"/>
+      <c r="E37" s="61"/>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="25"/>
-      <c r="E38" s="60"/>
+      <c r="E38" s="61"/>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="25"/>
-      <c r="E39" s="60"/>
+      <c r="E39" s="61"/>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="25"/>
-      <c r="E40" s="60"/>
+      <c r="E40" s="61"/>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="25"/>
-      <c r="E41" s="60"/>
+      <c r="E41" s="61"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="25"/>
-      <c r="E42" s="60"/>
+      <c r="E42" s="61"/>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="25"/>
-      <c r="E43" s="60"/>
+      <c r="E43" s="61"/>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="25"/>
-      <c r="E44" s="60"/>
+      <c r="E44" s="61"/>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="25"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="61"/>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="25"/>
-      <c r="E46" s="60"/>
+      <c r="E46" s="61"/>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="25"/>
-      <c r="E47" s="60"/>
+      <c r="E47" s="61"/>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="25"/>
-      <c r="E48" s="60"/>
+      <c r="E48" s="61"/>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="25"/>
-      <c r="E49" s="60"/>
+      <c r="E49" s="61"/>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="25"/>
-      <c r="E50" s="60"/>
+      <c r="E50" s="61"/>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="25"/>
-      <c r="E51" s="60"/>
+      <c r="E51" s="61"/>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="25"/>
-      <c r="E52" s="60"/>
+      <c r="E52" s="61"/>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="25"/>
-      <c r="E53" s="60"/>
+      <c r="E53" s="61"/>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="25"/>
-      <c r="E54" s="60"/>
+      <c r="E54" s="61"/>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="25"/>
-      <c r="E55" s="60"/>
+      <c r="E55" s="61"/>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="25"/>
-      <c r="E56" s="60"/>
+      <c r="E56" s="61"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="25"/>
-      <c r="E57" s="60"/>
+      <c r="E57" s="61"/>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="25"/>
-      <c r="E58" s="60"/>
+      <c r="E58" s="61"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="25"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="61"/>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="25"/>
-      <c r="E60" s="60"/>
+      <c r="E60" s="61"/>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="25"/>
-      <c r="E61" s="60"/>
+      <c r="E61" s="61"/>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="25"/>
-      <c r="E62" s="60"/>
+      <c r="E62" s="61"/>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="25"/>
-      <c r="E63" s="60"/>
+      <c r="E63" s="61"/>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="25"/>
-      <c r="E64" s="60"/>
+      <c r="E64" s="61"/>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="25"/>
-      <c r="E65" s="60"/>
+      <c r="E65" s="61"/>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="25"/>
-      <c r="E66" s="60"/>
+      <c r="E66" s="61"/>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="25"/>
-      <c r="E67" s="60"/>
+      <c r="E67" s="61"/>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="25"/>
-      <c r="E68" s="60"/>
+      <c r="E68" s="61"/>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="25"/>
-      <c r="E69" s="60"/>
+      <c r="E69" s="61"/>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="25"/>
-      <c r="E70" s="60"/>
+      <c r="E70" s="61"/>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="25"/>
-      <c r="E71" s="60"/>
+      <c r="E71" s="61"/>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="25"/>
-      <c r="E72" s="60"/>
+      <c r="E72" s="61"/>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="25"/>
-      <c r="E73" s="60"/>
+      <c r="E73" s="61"/>
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="25"/>
-      <c r="E74" s="60"/>
+      <c r="E74" s="61"/>
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="25"/>
-      <c r="E75" s="60"/>
+      <c r="E75" s="61"/>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="25"/>
-      <c r="E76" s="60"/>
+      <c r="E76" s="61"/>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="25"/>
-      <c r="E77" s="60"/>
+      <c r="E77" s="61"/>
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="25"/>
-      <c r="E78" s="60"/>
+      <c r="E78" s="61"/>
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="25"/>
-      <c r="E79" s="60"/>
+      <c r="E79" s="61"/>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="25"/>
-      <c r="E80" s="60"/>
+      <c r="E80" s="61"/>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="25"/>
-      <c r="E81" s="60"/>
+      <c r="E81" s="61"/>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="25"/>
-      <c r="E82" s="60"/>
+      <c r="E82" s="61"/>
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="25"/>
-      <c r="E83" s="60"/>
+      <c r="E83" s="61"/>
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="25"/>
-      <c r="E84" s="60"/>
+      <c r="E84" s="61"/>
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="25"/>
-      <c r="E85" s="60"/>
+      <c r="E85" s="61"/>
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="25"/>
-      <c r="E86" s="60"/>
+      <c r="E86" s="61"/>
     </row>
     <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="25"/>
-      <c r="E87" s="60"/>
+      <c r="E87" s="61"/>
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="25"/>
-      <c r="E88" s="60"/>
+      <c r="E88" s="61"/>
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="25"/>
-      <c r="E89" s="60"/>
+      <c r="E89" s="61"/>
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="25"/>
-      <c r="E90" s="60"/>
+      <c r="E90" s="61"/>
     </row>
     <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="25"/>
-      <c r="E91" s="60"/>
+      <c r="E91" s="61"/>
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="25"/>
-      <c r="E92" s="60"/>
+      <c r="E92" s="61"/>
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="25"/>
-      <c r="E93" s="60"/>
+      <c r="E93" s="61"/>
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="25"/>
-      <c r="E94" s="60"/>
+      <c r="E94" s="61"/>
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="25"/>
-      <c r="E95" s="60"/>
+      <c r="E95" s="61"/>
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="25"/>
-      <c r="E96" s="60"/>
+      <c r="E96" s="61"/>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="25"/>
-      <c r="E97" s="60"/>
+      <c r="E97" s="61"/>
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="25"/>
-      <c r="E98" s="60"/>
+      <c r="E98" s="61"/>
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="25"/>
-      <c r="E99" s="60"/>
+      <c r="E99" s="61"/>
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="25"/>
-      <c r="E100" s="60"/>
+      <c r="E100" s="61"/>
     </row>
     <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="25"/>
-      <c r="E101" s="60"/>
+      <c r="E101" s="61"/>
     </row>
     <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="25"/>
-      <c r="E102" s="60"/>
+      <c r="E102" s="61"/>
     </row>
     <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="25"/>
-      <c r="E103" s="60"/>
+      <c r="E103" s="61"/>
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="25"/>
-      <c r="E104" s="60"/>
+      <c r="E104" s="61"/>
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="25"/>
-      <c r="E105" s="60"/>
+      <c r="E105" s="61"/>
     </row>
     <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="25"/>
-      <c r="E106" s="60"/>
+      <c r="E106" s="61"/>
     </row>
     <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="25"/>
-      <c r="E107" s="60"/>
+      <c r="E107" s="61"/>
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="25"/>
-      <c r="E108" s="60"/>
+      <c r="E108" s="61"/>
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="25"/>
-      <c r="E109" s="60"/>
+      <c r="E109" s="61"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="25"/>
-      <c r="E110" s="60"/>
+      <c r="E110" s="61"/>
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="25"/>
-      <c r="E111" s="60"/>
+      <c r="E111" s="61"/>
     </row>
     <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="25"/>
-      <c r="E112" s="60"/>
+      <c r="E112" s="61"/>
     </row>
     <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="25"/>
-      <c r="E113" s="60"/>
+      <c r="E113" s="61"/>
     </row>
     <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="25"/>
-      <c r="E114" s="60"/>
+      <c r="E114" s="61"/>
     </row>
     <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="25"/>
-      <c r="E115" s="60"/>
+      <c r="E115" s="61"/>
     </row>
     <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="25"/>
-      <c r="E116" s="60"/>
+      <c r="E116" s="61"/>
     </row>
     <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="25"/>
-      <c r="E117" s="60"/>
+      <c r="E117" s="61"/>
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="25"/>
-      <c r="E118" s="60"/>
+      <c r="E118" s="61"/>
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="25"/>
-      <c r="E119" s="60"/>
+      <c r="E119" s="61"/>
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="25"/>
-      <c r="E120" s="60"/>
+      <c r="E120" s="61"/>
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="25"/>
-      <c r="E121" s="60"/>
+      <c r="E121" s="61"/>
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="25"/>
-      <c r="E122" s="60"/>
+      <c r="E122" s="61"/>
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="25"/>
-      <c r="E123" s="60"/>
+      <c r="E123" s="61"/>
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="25"/>
-      <c r="E124" s="60"/>
+      <c r="E124" s="61"/>
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="25"/>
-      <c r="E125" s="60"/>
+      <c r="E125" s="61"/>
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="25"/>
-      <c r="E126" s="60"/>
+      <c r="E126" s="61"/>
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="25"/>
-      <c r="E127" s="60"/>
+      <c r="E127" s="61"/>
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="25"/>
-      <c r="E128" s="60"/>
+      <c r="E128" s="61"/>
     </row>
     <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="25"/>
-      <c r="E129" s="60"/>
+      <c r="E129" s="61"/>
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="25"/>
-      <c r="E130" s="60"/>
+      <c r="E130" s="61"/>
     </row>
     <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="25"/>
-      <c r="E131" s="60"/>
+      <c r="E131" s="61"/>
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="25"/>
-      <c r="E132" s="60"/>
+      <c r="E132" s="61"/>
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="25"/>
-      <c r="E133" s="60"/>
+      <c r="E133" s="61"/>
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="25"/>
-      <c r="E134" s="60"/>
+      <c r="E134" s="61"/>
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="25"/>
-      <c r="E135" s="60"/>
+      <c r="E135" s="61"/>
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="25"/>
-      <c r="E136" s="60"/>
+      <c r="E136" s="61"/>
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="25"/>
-      <c r="E137" s="60"/>
+      <c r="E137" s="61"/>
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="25"/>
-      <c r="E138" s="60"/>
+      <c r="E138" s="61"/>
     </row>
     <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="25"/>
-      <c r="E139" s="60"/>
+      <c r="E139" s="61"/>
     </row>
     <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="25"/>
-      <c r="E140" s="60"/>
+      <c r="E140" s="61"/>
     </row>
     <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="25"/>
-      <c r="E141" s="60"/>
+      <c r="E141" s="61"/>
     </row>
     <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="25"/>
-      <c r="E142" s="60"/>
+      <c r="E142" s="61"/>
     </row>
     <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="25"/>
-      <c r="E143" s="60"/>
+      <c r="E143" s="61"/>
     </row>
     <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="25"/>
-      <c r="E144" s="60"/>
+      <c r="E144" s="61"/>
     </row>
     <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="25"/>
-      <c r="E145" s="60"/>
+      <c r="E145" s="61"/>
     </row>
     <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="25"/>
-      <c r="E146" s="60"/>
+      <c r="E146" s="61"/>
     </row>
     <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="25"/>
-      <c r="E147" s="60"/>
+      <c r="E147" s="61"/>
     </row>
     <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="25"/>
-      <c r="E148" s="60"/>
+      <c r="E148" s="61"/>
     </row>
     <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="25"/>
-      <c r="E149" s="60"/>
+      <c r="E149" s="61"/>
     </row>
     <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="25"/>
-      <c r="E150" s="60"/>
+      <c r="E150" s="61"/>
     </row>
     <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="25"/>
-      <c r="E151" s="60"/>
+      <c r="E151" s="61"/>
     </row>
     <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="25"/>
-      <c r="E152" s="60"/>
+      <c r="E152" s="61"/>
     </row>
     <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="25"/>
-      <c r="E153" s="60"/>
+      <c r="E153" s="61"/>
     </row>
     <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="25"/>
-      <c r="E154" s="60"/>
+      <c r="E154" s="61"/>
     </row>
     <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="25"/>
-      <c r="E155" s="60"/>
+      <c r="E155" s="61"/>
     </row>
     <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="25"/>
-      <c r="E156" s="60"/>
+      <c r="E156" s="61"/>
     </row>
     <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="25"/>
-      <c r="E157" s="60"/>
+      <c r="E157" s="61"/>
     </row>
     <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="25"/>
-      <c r="E158" s="60"/>
+      <c r="E158" s="61"/>
     </row>
     <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="25"/>
-      <c r="E159" s="60"/>
+      <c r="E159" s="61"/>
     </row>
     <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="25"/>
-      <c r="E160" s="60"/>
+      <c r="E160" s="61"/>
     </row>
     <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="25"/>
-      <c r="E161" s="60"/>
+      <c r="E161" s="61"/>
     </row>
     <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="25"/>
-      <c r="E162" s="60"/>
+      <c r="E162" s="61"/>
     </row>
     <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="25"/>
-      <c r="E163" s="60"/>
+      <c r="E163" s="61"/>
     </row>
     <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="25"/>
-      <c r="E164" s="60"/>
+      <c r="E164" s="61"/>
     </row>
     <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="25"/>
-      <c r="E165" s="60"/>
+      <c r="E165" s="61"/>
     </row>
     <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="25"/>
-      <c r="E166" s="60"/>
+      <c r="E166" s="61"/>
     </row>
     <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="25"/>
-      <c r="E167" s="60"/>
+      <c r="E167" s="61"/>
     </row>
     <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="25"/>
-      <c r="E168" s="60"/>
+      <c r="E168" s="61"/>
     </row>
     <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="25"/>
-      <c r="E169" s="60"/>
+      <c r="E169" s="61"/>
     </row>
     <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="25"/>
-      <c r="E170" s="60"/>
+      <c r="E170" s="61"/>
     </row>
     <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="25"/>
-      <c r="E171" s="60"/>
+      <c r="E171" s="61"/>
     </row>
     <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="25"/>
-      <c r="E172" s="60"/>
+      <c r="E172" s="61"/>
     </row>
     <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="25"/>
-      <c r="E173" s="60"/>
+      <c r="E173" s="61"/>
     </row>
     <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="25"/>
-      <c r="E174" s="60"/>
+      <c r="E174" s="61"/>
     </row>
     <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="25"/>
-      <c r="E175" s="60"/>
+      <c r="E175" s="61"/>
     </row>
     <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="25"/>
-      <c r="E176" s="60"/>
+      <c r="E176" s="61"/>
     </row>
     <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="25"/>
-      <c r="E177" s="60"/>
+      <c r="E177" s="61"/>
     </row>
     <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="25"/>
-      <c r="E178" s="60"/>
+      <c r="E178" s="61"/>
     </row>
     <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="25"/>
-      <c r="E179" s="60"/>
+      <c r="E179" s="61"/>
     </row>
     <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="25"/>
-      <c r="E180" s="60"/>
+      <c r="E180" s="61"/>
     </row>
     <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="25"/>
-      <c r="E181" s="60"/>
+      <c r="E181" s="61"/>
     </row>
     <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="25"/>
-      <c r="E182" s="60"/>
+      <c r="E182" s="61"/>
     </row>
     <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="25"/>
-      <c r="E183" s="60"/>
+      <c r="E183" s="61"/>
     </row>
     <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="25"/>
-      <c r="E184" s="60"/>
+      <c r="E184" s="61"/>
     </row>
     <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="25"/>
-      <c r="E185" s="60"/>
+      <c r="E185" s="61"/>
     </row>
     <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="25"/>
-      <c r="E186" s="60"/>
+      <c r="E186" s="61"/>
     </row>
     <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="25"/>
-      <c r="E187" s="60"/>
+      <c r="E187" s="61"/>
     </row>
     <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="25"/>
-      <c r="E188" s="60"/>
+      <c r="E188" s="61"/>
     </row>
     <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="25"/>
-      <c r="E189" s="60"/>
+      <c r="E189" s="61"/>
     </row>
     <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="25"/>
-      <c r="E190" s="60"/>
+      <c r="E190" s="61"/>
     </row>
     <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="25"/>
-      <c r="E191" s="60"/>
+      <c r="E191" s="61"/>
     </row>
     <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="25"/>
-      <c r="E192" s="60"/>
+      <c r="E192" s="61"/>
     </row>
     <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="25"/>
-      <c r="E193" s="60"/>
+      <c r="E193" s="61"/>
     </row>
     <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="25"/>
-      <c r="E194" s="60"/>
+      <c r="E194" s="61"/>
     </row>
     <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="25"/>
-      <c r="E195" s="60"/>
+      <c r="E195" s="61"/>
     </row>
     <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="25"/>
-      <c r="E196" s="60"/>
+      <c r="E196" s="61"/>
     </row>
     <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="25"/>
-      <c r="E197" s="60"/>
+      <c r="E197" s="61"/>
     </row>
     <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="25"/>
-      <c r="E198" s="60"/>
+      <c r="E198" s="61"/>
     </row>
     <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="25"/>
-      <c r="E199" s="60"/>
+      <c r="E199" s="61"/>
     </row>
     <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="25"/>
-      <c r="E200" s="60"/>
+      <c r="E200" s="61"/>
     </row>
     <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="25"/>
-      <c r="E201" s="60"/>
+      <c r="E201" s="61"/>
     </row>
     <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="25"/>
-      <c r="E202" s="60"/>
+      <c r="E202" s="61"/>
     </row>
     <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="25"/>
-      <c r="E203" s="60"/>
+      <c r="E203" s="61"/>
     </row>
     <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="25"/>
-      <c r="E204" s="60"/>
+      <c r="E204" s="61"/>
     </row>
     <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="25"/>
-      <c r="E205" s="60"/>
+      <c r="E205" s="61"/>
     </row>
     <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="25"/>
-      <c r="E206" s="60"/>
+      <c r="E206" s="61"/>
     </row>
     <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="25"/>
-      <c r="E207" s="60"/>
+      <c r="E207" s="61"/>
     </row>
     <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="25"/>
-      <c r="E208" s="60"/>
+      <c r="E208" s="61"/>
     </row>
     <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="25"/>
-      <c r="E209" s="60"/>
+      <c r="E209" s="61"/>
     </row>
     <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="25"/>
-      <c r="E210" s="60"/>
+      <c r="E210" s="61"/>
     </row>
     <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="25"/>
-      <c r="E211" s="60"/>
+      <c r="E211" s="61"/>
     </row>
     <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="25"/>
-      <c r="E212" s="60"/>
+      <c r="E212" s="61"/>
     </row>
     <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="25"/>
-      <c r="E213" s="60"/>
+      <c r="E213" s="61"/>
     </row>
     <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="25"/>
-      <c r="E214" s="60"/>
+      <c r="E214" s="61"/>
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="25"/>
-      <c r="E215" s="60"/>
+      <c r="E215" s="61"/>
     </row>
     <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="25"/>
-      <c r="E216" s="60"/>
+      <c r="E216" s="61"/>
     </row>
     <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="25"/>
-      <c r="E217" s="60"/>
+      <c r="E217" s="61"/>
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="25"/>
-      <c r="E218" s="60"/>
+      <c r="E218" s="61"/>
     </row>
     <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="25"/>
-      <c r="E219" s="60"/>
+      <c r="E219" s="61"/>
     </row>
     <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="25"/>
-      <c r="E220" s="60"/>
+      <c r="E220" s="61"/>
     </row>
     <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="25"/>
-      <c r="E221" s="60"/>
+      <c r="E221" s="61"/>
     </row>
     <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="25"/>
-      <c r="E222" s="60"/>
+      <c r="E222" s="61"/>
     </row>
     <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="25"/>
-      <c r="E223" s="60"/>
+      <c r="E223" s="61"/>
     </row>
     <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="25"/>
-      <c r="E224" s="60"/>
+      <c r="E224" s="61"/>
     </row>
     <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="25"/>
-      <c r="E225" s="60"/>
+      <c r="E225" s="61"/>
     </row>
     <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="25"/>
-      <c r="E226" s="60"/>
+      <c r="E226" s="61"/>
     </row>
     <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="25"/>
-      <c r="E227" s="60"/>
+      <c r="E227" s="61"/>
     </row>
     <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="25"/>
-      <c r="E228" s="60"/>
+      <c r="E228" s="61"/>
     </row>
     <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="25"/>
-      <c r="E229" s="60"/>
+      <c r="E229" s="61"/>
     </row>
     <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="25"/>
-      <c r="E230" s="60"/>
+      <c r="E230" s="61"/>
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="25"/>
-      <c r="E231" s="60"/>
+      <c r="E231" s="61"/>
     </row>
     <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="25"/>
-      <c r="E232" s="60"/>
+      <c r="E232" s="61"/>
     </row>
     <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="25"/>
-      <c r="E233" s="60"/>
+      <c r="E233" s="61"/>
     </row>
     <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="25"/>
-      <c r="E234" s="60"/>
+      <c r="E234" s="61"/>
     </row>
     <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="25"/>
-      <c r="E235" s="60"/>
+      <c r="E235" s="61"/>
     </row>
     <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="25"/>
-      <c r="E236" s="60"/>
+      <c r="E236" s="61"/>
     </row>
     <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="25"/>
-      <c r="E237" s="60"/>
+      <c r="E237" s="61"/>
     </row>
     <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="25"/>
-      <c r="E238" s="60"/>
+      <c r="E238" s="61"/>
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="25"/>
-      <c r="E239" s="60"/>
+      <c r="E239" s="61"/>
     </row>
     <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="25"/>
-      <c r="E240" s="60"/>
+      <c r="E240" s="61"/>
     </row>
     <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="25"/>
-      <c r="E241" s="60"/>
+      <c r="E241" s="61"/>
     </row>
     <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="25"/>
-      <c r="E242" s="60"/>
+      <c r="E242" s="61"/>
     </row>
     <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="25"/>
-      <c r="E243" s="60"/>
+      <c r="E243" s="61"/>
     </row>
     <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="25"/>
-      <c r="E244" s="60"/>
+      <c r="E244" s="61"/>
     </row>
     <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="25"/>
-      <c r="E245" s="60"/>
+      <c r="E245" s="61"/>
     </row>
     <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="25"/>
-      <c r="E246" s="60"/>
+      <c r="E246" s="61"/>
     </row>
     <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="25"/>
-      <c r="E247" s="60"/>
+      <c r="E247" s="61"/>
     </row>
     <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="25"/>
-      <c r="E248" s="60"/>
+      <c r="E248" s="61"/>
     </row>
     <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="25"/>
-      <c r="E249" s="60"/>
+      <c r="E249" s="61"/>
     </row>
     <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="25"/>
-      <c r="E250" s="60"/>
+      <c r="E250" s="61"/>
     </row>
     <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="25"/>
-      <c r="E251" s="60"/>
+      <c r="E251" s="61"/>
     </row>
     <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="25"/>
-      <c r="E252" s="60"/>
+      <c r="E252" s="61"/>
     </row>
     <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="25"/>
-      <c r="E253" s="60"/>
+      <c r="E253" s="61"/>
     </row>
     <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="25"/>
-      <c r="E254" s="60"/>
+      <c r="E254" s="61"/>
     </row>
     <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="25"/>
-      <c r="E255" s="60"/>
+      <c r="E255" s="61"/>
     </row>
     <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="25"/>
-      <c r="E256" s="60"/>
+      <c r="E256" s="61"/>
     </row>
     <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="25"/>
-      <c r="E257" s="60"/>
+      <c r="E257" s="61"/>
     </row>
     <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="25"/>
-      <c r="E258" s="60"/>
+      <c r="E258" s="61"/>
     </row>
     <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="25"/>
-      <c r="E259" s="60"/>
+      <c r="E259" s="61"/>
     </row>
     <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="25"/>
-      <c r="E260" s="60"/>
+      <c r="E260" s="61"/>
     </row>
     <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="25"/>
-      <c r="E261" s="60"/>
+      <c r="E261" s="61"/>
     </row>
     <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="25"/>
-      <c r="E262" s="60"/>
+      <c r="E262" s="61"/>
     </row>
     <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="25"/>
-      <c r="E263" s="60"/>
+      <c r="E263" s="61"/>
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="25"/>
-      <c r="E264" s="60"/>
+      <c r="E264" s="61"/>
     </row>
     <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="25"/>
-      <c r="E265" s="60"/>
+      <c r="E265" s="61"/>
     </row>
     <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="25"/>
-      <c r="E266" s="60"/>
+      <c r="E266" s="61"/>
     </row>
     <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="25"/>
-      <c r="E267" s="60"/>
+      <c r="E267" s="61"/>
     </row>
     <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="25"/>
-      <c r="E268" s="60"/>
+      <c r="E268" s="61"/>
     </row>
     <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="25"/>
-      <c r="E269" s="60"/>
+      <c r="E269" s="61"/>
     </row>
     <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="25"/>
-      <c r="E270" s="60"/>
+      <c r="E270" s="61"/>
     </row>
     <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="25"/>
-      <c r="E271" s="60"/>
+      <c r="E271" s="61"/>
     </row>
     <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="25"/>
-      <c r="E272" s="60"/>
+      <c r="E272" s="61"/>
     </row>
     <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="25"/>
-      <c r="E273" s="60"/>
+      <c r="E273" s="61"/>
     </row>
     <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="25"/>
-      <c r="E274" s="60"/>
+      <c r="E274" s="61"/>
     </row>
     <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="25"/>
-      <c r="E275" s="60"/>
+      <c r="E275" s="61"/>
     </row>
     <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="25"/>
-      <c r="E276" s="60"/>
+      <c r="E276" s="61"/>
     </row>
     <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="25"/>
-      <c r="E277" s="60"/>
+      <c r="E277" s="61"/>
     </row>
     <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="25"/>
-      <c r="E278" s="60"/>
+      <c r="E278" s="61"/>
     </row>
     <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="25"/>
-      <c r="E279" s="60"/>
+      <c r="E279" s="61"/>
     </row>
     <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="25"/>
-      <c r="E280" s="60"/>
+      <c r="E280" s="61"/>
     </row>
     <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="25"/>
-      <c r="E281" s="60"/>
+      <c r="E281" s="61"/>
     </row>
     <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="25"/>
-      <c r="E282" s="60"/>
+      <c r="E282" s="61"/>
     </row>
     <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="25"/>
-      <c r="E283" s="60"/>
+      <c r="E283" s="61"/>
     </row>
     <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="25"/>
-      <c r="E284" s="60"/>
+      <c r="E284" s="61"/>
     </row>
     <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="25"/>
-      <c r="E285" s="60"/>
+      <c r="E285" s="61"/>
     </row>
     <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="25"/>
-      <c r="E286" s="60"/>
+      <c r="E286" s="61"/>
     </row>
     <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="25"/>
-      <c r="E287" s="60"/>
+      <c r="E287" s="61"/>
     </row>
     <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="25"/>
-      <c r="E288" s="60"/>
+      <c r="E288" s="61"/>
     </row>
     <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="25"/>
-      <c r="E289" s="60"/>
+      <c r="E289" s="61"/>
     </row>
     <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="25"/>
-      <c r="E290" s="60"/>
+      <c r="E290" s="61"/>
     </row>
     <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="25"/>
-      <c r="E291" s="60"/>
+      <c r="E291" s="61"/>
     </row>
     <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="25"/>
-      <c r="E292" s="60"/>
+      <c r="E292" s="61"/>
     </row>
     <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="25"/>
-      <c r="E293" s="60"/>
+      <c r="E293" s="61"/>
     </row>
     <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="25"/>
-      <c r="E294" s="60"/>
+      <c r="E294" s="61"/>
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="25"/>
-      <c r="E295" s="60"/>
+      <c r="E295" s="61"/>
     </row>
     <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="25"/>
-      <c r="E296" s="60"/>
+      <c r="E296" s="61"/>
     </row>
     <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="25"/>
-      <c r="E297" s="60"/>
+      <c r="E297" s="61"/>
     </row>
     <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="25"/>
-      <c r="E298" s="60"/>
+      <c r="E298" s="61"/>
     </row>
     <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="25"/>
-      <c r="E299" s="60"/>
+      <c r="E299" s="61"/>
     </row>
     <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="25"/>
-      <c r="E300" s="60"/>
+      <c r="E300" s="61"/>
     </row>
     <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="25"/>
-      <c r="E301" s="60"/>
+      <c r="E301" s="61"/>
     </row>
     <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="25"/>
-      <c r="E302" s="60"/>
+      <c r="E302" s="61"/>
     </row>
     <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="25"/>
-      <c r="E303" s="60"/>
+      <c r="E303" s="61"/>
     </row>
     <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="25"/>
-      <c r="E304" s="60"/>
+      <c r="E304" s="61"/>
     </row>
     <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="25"/>
-      <c r="E305" s="60"/>
+      <c r="E305" s="61"/>
     </row>
     <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="25"/>
-      <c r="E306" s="60"/>
+      <c r="E306" s="61"/>
     </row>
     <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="25"/>
-      <c r="E307" s="60"/>
+      <c r="E307" s="61"/>
     </row>
     <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="25"/>
-      <c r="E308" s="60"/>
+      <c r="E308" s="61"/>
     </row>
     <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="25"/>
-      <c r="E309" s="60"/>
+      <c r="E309" s="61"/>
     </row>
     <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="25"/>
-      <c r="E310" s="60"/>
+      <c r="E310" s="61"/>
     </row>
     <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="25"/>
-      <c r="E311" s="60"/>
+      <c r="E311" s="61"/>
     </row>
     <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="25"/>
-      <c r="E312" s="60"/>
+      <c r="E312" s="61"/>
     </row>
     <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="25"/>
-      <c r="E313" s="60"/>
+      <c r="E313" s="61"/>
     </row>
     <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="25"/>
-      <c r="E314" s="60"/>
+      <c r="E314" s="61"/>
     </row>
     <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="25"/>
-      <c r="E315" s="60"/>
+      <c r="E315" s="61"/>
     </row>
     <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="25"/>
-      <c r="E316" s="60"/>
+      <c r="E316" s="61"/>
     </row>
     <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="25"/>
-      <c r="E317" s="60"/>
+      <c r="E317" s="61"/>
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="25"/>
-      <c r="E318" s="60"/>
+      <c r="E318" s="61"/>
     </row>
     <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="25"/>
-      <c r="E319" s="60"/>
+      <c r="E319" s="61"/>
     </row>
     <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="25"/>
-      <c r="E320" s="60"/>
+      <c r="E320" s="61"/>
     </row>
     <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="25"/>
-      <c r="E321" s="60"/>
+      <c r="E321" s="61"/>
     </row>
     <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="25"/>
-      <c r="E322" s="60"/>
+      <c r="E322" s="61"/>
     </row>
     <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="25"/>
-      <c r="E323" s="60"/>
+      <c r="E323" s="61"/>
     </row>
     <row r="324" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="25"/>
-      <c r="E324" s="60"/>
+      <c r="E324" s="61"/>
     </row>
     <row r="325" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="25"/>
-      <c r="E325" s="60"/>
+      <c r="E325" s="61"/>
     </row>
     <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="25"/>
-      <c r="E326" s="60"/>
+      <c r="E326" s="61"/>
     </row>
     <row r="327" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="25"/>
-      <c r="E327" s="60"/>
+      <c r="E327" s="61"/>
     </row>
     <row r="328" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="25"/>
-      <c r="E328" s="60"/>
+      <c r="E328" s="61"/>
     </row>
     <row r="329" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="25"/>
-      <c r="E329" s="60"/>
+      <c r="E329" s="61"/>
     </row>
     <row r="330" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="25"/>
-      <c r="E330" s="60"/>
+      <c r="E330" s="61"/>
     </row>
     <row r="331" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="25"/>
-      <c r="E331" s="60"/>
+      <c r="E331" s="61"/>
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="25"/>
-      <c r="E332" s="60"/>
+      <c r="E332" s="61"/>
     </row>
     <row r="333" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="25"/>
-      <c r="E333" s="60"/>
+      <c r="E333" s="61"/>
     </row>
     <row r="334" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="25"/>
-      <c r="E334" s="60"/>
+      <c r="E334" s="61"/>
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="25"/>
-      <c r="E335" s="60"/>
+      <c r="E335" s="61"/>
     </row>
     <row r="336" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="25"/>
-      <c r="E336" s="60"/>
+      <c r="E336" s="61"/>
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="25"/>
-      <c r="E337" s="60"/>
+      <c r="E337" s="61"/>
     </row>
     <row r="338" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="25"/>
-      <c r="E338" s="60"/>
+      <c r="E338" s="61"/>
     </row>
     <row r="339" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="25"/>
-      <c r="E339" s="60"/>
+      <c r="E339" s="61"/>
     </row>
     <row r="340" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="25"/>
-      <c r="E340" s="60"/>
+      <c r="E340" s="61"/>
     </row>
     <row r="341" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="25"/>
-      <c r="E341" s="60"/>
+      <c r="E341" s="61"/>
     </row>
     <row r="342" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="25"/>
-      <c r="E342" s="60"/>
+      <c r="E342" s="61"/>
     </row>
     <row r="343" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="25"/>
-      <c r="E343" s="60"/>
+      <c r="E343" s="61"/>
     </row>
     <row r="344" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="25"/>
-      <c r="E344" s="60"/>
+      <c r="E344" s="61"/>
     </row>
     <row r="345" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="25"/>
-      <c r="E345" s="60"/>
+      <c r="E345" s="61"/>
     </row>
     <row r="346" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="25"/>
-      <c r="E346" s="60"/>
+      <c r="E346" s="61"/>
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="25"/>
-      <c r="E347" s="60"/>
+      <c r="E347" s="61"/>
     </row>
     <row r="348" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="25"/>
-      <c r="E348" s="60"/>
+      <c r="E348" s="61"/>
     </row>
     <row r="349" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="25"/>
-      <c r="E349" s="60"/>
+      <c r="E349" s="61"/>
     </row>
     <row r="350" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="25"/>
-      <c r="E350" s="60"/>
+      <c r="E350" s="61"/>
     </row>
     <row r="351" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="25"/>
-      <c r="E351" s="60"/>
+      <c r="E351" s="61"/>
     </row>
     <row r="352" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="25"/>
-      <c r="E352" s="60"/>
+      <c r="E352" s="61"/>
     </row>
     <row r="353" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="25"/>
-      <c r="E353" s="60"/>
+      <c r="E353" s="61"/>
     </row>
     <row r="354" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="25"/>
-      <c r="E354" s="60"/>
+      <c r="E354" s="61"/>
     </row>
     <row r="355" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="25"/>
-      <c r="E355" s="60"/>
+      <c r="E355" s="61"/>
     </row>
     <row r="356" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="25"/>
-      <c r="E356" s="60"/>
+      <c r="E356" s="61"/>
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="25"/>
-      <c r="E357" s="60"/>
+      <c r="E357" s="61"/>
     </row>
     <row r="358" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="25"/>
-      <c r="E358" s="60"/>
+      <c r="E358" s="61"/>
     </row>
     <row r="359" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="25"/>
-      <c r="E359" s="60"/>
+      <c r="E359" s="61"/>
     </row>
     <row r="360" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="25"/>
-      <c r="E360" s="60"/>
+      <c r="E360" s="61"/>
     </row>
     <row r="361" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="25"/>
-      <c r="E361" s="60"/>
+      <c r="E361" s="61"/>
     </row>
     <row r="362" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="25"/>
-      <c r="E362" s="60"/>
+      <c r="E362" s="61"/>
     </row>
     <row r="363" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="25"/>
-      <c r="E363" s="60"/>
+      <c r="E363" s="61"/>
     </row>
     <row r="364" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="25"/>
-      <c r="E364" s="60"/>
+      <c r="E364" s="61"/>
     </row>
     <row r="365" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="25"/>
-      <c r="E365" s="60"/>
+      <c r="E365" s="61"/>
     </row>
     <row r="366" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="25"/>
-      <c r="E366" s="60"/>
+      <c r="E366" s="61"/>
     </row>
     <row r="367" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="25"/>
-      <c r="E367" s="60"/>
+      <c r="E367" s="61"/>
     </row>
     <row r="368" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="25"/>
-      <c r="E368" s="60"/>
+      <c r="E368" s="61"/>
     </row>
     <row r="369" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="25"/>
-      <c r="E369" s="60"/>
+      <c r="E369" s="61"/>
     </row>
     <row r="370" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="25"/>
-      <c r="E370" s="60"/>
+      <c r="E370" s="61"/>
     </row>
     <row r="371" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="25"/>
-      <c r="E371" s="60"/>
+      <c r="E371" s="61"/>
     </row>
     <row r="372" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="25"/>
-      <c r="E372" s="60"/>
+      <c r="E372" s="61"/>
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="25"/>
-      <c r="E373" s="60"/>
+      <c r="E373" s="61"/>
     </row>
     <row r="374" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="25"/>
-      <c r="E374" s="60"/>
+      <c r="E374" s="61"/>
     </row>
     <row r="375" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="25"/>
-      <c r="E375" s="60"/>
+      <c r="E375" s="61"/>
     </row>
     <row r="376" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="25"/>
-      <c r="E376" s="60"/>
+      <c r="E376" s="61"/>
     </row>
     <row r="377" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="25"/>
-      <c r="E377" s="60"/>
+      <c r="E377" s="61"/>
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="25"/>
-      <c r="E378" s="60"/>
+      <c r="E378" s="61"/>
     </row>
     <row r="379" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="25"/>
-      <c r="E379" s="60"/>
+      <c r="E379" s="61"/>
     </row>
     <row r="380" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="25"/>
-      <c r="E380" s="60"/>
+      <c r="E380" s="61"/>
     </row>
     <row r="381" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="25"/>
-      <c r="E381" s="60"/>
+      <c r="E381" s="61"/>
     </row>
     <row r="382" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="25"/>
-      <c r="E382" s="60"/>
+      <c r="E382" s="61"/>
     </row>
     <row r="383" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="25"/>
-      <c r="E383" s="60"/>
+      <c r="E383" s="61"/>
     </row>
     <row r="384" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="25"/>
-      <c r="E384" s="60"/>
+      <c r="E384" s="61"/>
     </row>
     <row r="385" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="25"/>
-      <c r="E385" s="60"/>
+      <c r="E385" s="61"/>
     </row>
     <row r="386" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="25"/>
-      <c r="E386" s="60"/>
+      <c r="E386" s="61"/>
     </row>
     <row r="387" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="25"/>
-      <c r="E387" s="60"/>
+      <c r="E387" s="61"/>
     </row>
     <row r="388" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="25"/>
-      <c r="E388" s="60"/>
+      <c r="E388" s="61"/>
     </row>
     <row r="389" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="25"/>
-      <c r="E389" s="60"/>
+      <c r="E389" s="61"/>
     </row>
     <row r="390" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="25"/>
-      <c r="E390" s="60"/>
+      <c r="E390" s="61"/>
     </row>
     <row r="391" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="25"/>
-      <c r="E391" s="60"/>
+      <c r="E391" s="61"/>
     </row>
     <row r="392" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="25"/>
-      <c r="E392" s="60"/>
+      <c r="E392" s="61"/>
     </row>
     <row r="393" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="25"/>
-      <c r="E393" s="60"/>
+      <c r="E393" s="61"/>
     </row>
     <row r="394" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="25"/>
-      <c r="E394" s="60"/>
+      <c r="E394" s="61"/>
     </row>
     <row r="395" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="25"/>
-      <c r="E395" s="60"/>
+      <c r="E395" s="61"/>
     </row>
     <row r="396" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="25"/>
-      <c r="E396" s="60"/>
+      <c r="E396" s="61"/>
     </row>
     <row r="397" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="25"/>
-      <c r="E397" s="60"/>
+      <c r="E397" s="61"/>
     </row>
     <row r="398" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="25"/>
-      <c r="E398" s="60"/>
+      <c r="E398" s="61"/>
     </row>
     <row r="399" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="25"/>
-      <c r="E399" s="60"/>
+      <c r="E399" s="61"/>
     </row>
     <row r="400" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="25"/>
-      <c r="E400" s="60"/>
+      <c r="E400" s="61"/>
     </row>
     <row r="401" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="25"/>
-      <c r="E401" s="60"/>
+      <c r="E401" s="61"/>
     </row>
     <row r="402" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="25"/>
-      <c r="E402" s="60"/>
+      <c r="E402" s="61"/>
     </row>
     <row r="403" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="25"/>
-      <c r="E403" s="60"/>
+      <c r="E403" s="61"/>
     </row>
     <row r="404" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="25"/>
-      <c r="E404" s="60"/>
+      <c r="E404" s="61"/>
     </row>
     <row r="405" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="25"/>
-      <c r="E405" s="60"/>
+      <c r="E405" s="61"/>
     </row>
     <row r="406" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="25"/>
-      <c r="E406" s="60"/>
+      <c r="E406" s="61"/>
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="25"/>
-      <c r="E407" s="60"/>
+      <c r="E407" s="61"/>
     </row>
     <row r="408" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="25"/>
-      <c r="E408" s="60"/>
+      <c r="E408" s="61"/>
     </row>
     <row r="409" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="25"/>
-      <c r="E409" s="60"/>
+      <c r="E409" s="61"/>
     </row>
     <row r="410" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="25"/>
-      <c r="E410" s="60"/>
+      <c r="E410" s="61"/>
     </row>
     <row r="411" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="25"/>
-      <c r="E411" s="60"/>
+      <c r="E411" s="61"/>
     </row>
     <row r="412" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="25"/>
-      <c r="E412" s="60"/>
+      <c r="E412" s="61"/>
     </row>
     <row r="413" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="25"/>
-      <c r="E413" s="60"/>
+      <c r="E413" s="61"/>
     </row>
     <row r="414" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="25"/>
-      <c r="E414" s="60"/>
+      <c r="E414" s="61"/>
     </row>
     <row r="415" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="25"/>
-      <c r="E415" s="60"/>
+      <c r="E415" s="61"/>
     </row>
     <row r="416" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="25"/>
-      <c r="E416" s="60"/>
+      <c r="E416" s="61"/>
     </row>
     <row r="417" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="25"/>
-      <c r="E417" s="60"/>
+      <c r="E417" s="61"/>
     </row>
     <row r="418" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="25"/>
-      <c r="E418" s="60"/>
+      <c r="E418" s="61"/>
     </row>
     <row r="419" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="25"/>
-      <c r="E419" s="60"/>
+      <c r="E419" s="61"/>
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="25"/>
-      <c r="E420" s="60"/>
+      <c r="E420" s="61"/>
     </row>
     <row r="421" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="25"/>
-      <c r="E421" s="60"/>
+      <c r="E421" s="61"/>
     </row>
     <row r="422" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="25"/>
-      <c r="E422" s="60"/>
+      <c r="E422" s="61"/>
     </row>
     <row r="423" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="25"/>
-      <c r="E423" s="60"/>
+      <c r="E423" s="61"/>
     </row>
     <row r="424" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="25"/>
-      <c r="E424" s="60"/>
+      <c r="E424" s="61"/>
     </row>
     <row r="425" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="25"/>
-      <c r="E425" s="60"/>
+      <c r="E425" s="61"/>
     </row>
     <row r="426" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="25"/>
-      <c r="E426" s="60"/>
+      <c r="E426" s="61"/>
     </row>
     <row r="427" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="25"/>
-      <c r="E427" s="60"/>
+      <c r="E427" s="61"/>
     </row>
     <row r="428" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="25"/>
-      <c r="E428" s="60"/>
+      <c r="E428" s="61"/>
     </row>
     <row r="429" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="25"/>
-      <c r="E429" s="60"/>
+      <c r="E429" s="61"/>
     </row>
     <row r="430" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="25"/>
-      <c r="E430" s="60"/>
+      <c r="E430" s="61"/>
     </row>
     <row r="431" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="25"/>
-      <c r="E431" s="60"/>
+      <c r="E431" s="61"/>
     </row>
     <row r="432" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="25"/>
-      <c r="E432" s="60"/>
+      <c r="E432" s="61"/>
     </row>
     <row r="433" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="25"/>
-      <c r="E433" s="60"/>
+      <c r="E433" s="61"/>
     </row>
     <row r="434" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="25"/>
-      <c r="E434" s="60"/>
+      <c r="E434" s="61"/>
     </row>
     <row r="435" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="25"/>
-      <c r="E435" s="60"/>
+      <c r="E435" s="61"/>
     </row>
     <row r="436" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="25"/>
-      <c r="E436" s="60"/>
+      <c r="E436" s="61"/>
     </row>
     <row r="437" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="25"/>
-      <c r="E437" s="60"/>
+      <c r="E437" s="61"/>
     </row>
     <row r="438" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="25"/>
-      <c r="E438" s="60"/>
+      <c r="E438" s="61"/>
     </row>
     <row r="439" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="25"/>
-      <c r="E439" s="60"/>
+      <c r="E439" s="61"/>
     </row>
     <row r="440" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="25"/>
-      <c r="E440" s="60"/>
+      <c r="E440" s="61"/>
     </row>
     <row r="441" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="25"/>
-      <c r="E441" s="60"/>
+      <c r="E441" s="61"/>
     </row>
     <row r="442" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="25"/>
-      <c r="E442" s="60"/>
+      <c r="E442" s="61"/>
     </row>
     <row r="443" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="25"/>
-      <c r="E443" s="60"/>
+      <c r="E443" s="61"/>
     </row>
     <row r="444" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="25"/>
-      <c r="E444" s="60"/>
+      <c r="E444" s="61"/>
     </row>
     <row r="445" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="25"/>
-      <c r="E445" s="60"/>
+      <c r="E445" s="61"/>
     </row>
     <row r="446" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="25"/>
-      <c r="E446" s="60"/>
+      <c r="E446" s="61"/>
     </row>
     <row r="447" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="25"/>
-      <c r="E447" s="60"/>
+      <c r="E447" s="61"/>
     </row>
     <row r="448" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="25"/>
-      <c r="E448" s="60"/>
+      <c r="E448" s="61"/>
     </row>
     <row r="449" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="25"/>
-      <c r="E449" s="60"/>
+      <c r="E449" s="61"/>
     </row>
     <row r="450" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="25"/>
-      <c r="E450" s="60"/>
+      <c r="E450" s="61"/>
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="25"/>
-      <c r="E451" s="60"/>
+      <c r="E451" s="61"/>
     </row>
     <row r="452" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="25"/>
-      <c r="E452" s="60"/>
+      <c r="E452" s="61"/>
     </row>
     <row r="453" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="25"/>
-      <c r="E453" s="60"/>
+      <c r="E453" s="61"/>
     </row>
     <row r="454" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="25"/>
-      <c r="E454" s="60"/>
+      <c r="E454" s="61"/>
     </row>
     <row r="455" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="25"/>
-      <c r="E455" s="60"/>
+      <c r="E455" s="61"/>
     </row>
     <row r="456" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="25"/>
-      <c r="E456" s="60"/>
+      <c r="E456" s="61"/>
     </row>
     <row r="457" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="25"/>
-      <c r="E457" s="60"/>
+      <c r="E457" s="61"/>
     </row>
     <row r="458" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="25"/>
-      <c r="E458" s="60"/>
+      <c r="E458" s="61"/>
     </row>
     <row r="459" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="25"/>
-      <c r="E459" s="60"/>
+      <c r="E459" s="61"/>
     </row>
     <row r="460" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="25"/>
-      <c r="E460" s="60"/>
+      <c r="E460" s="61"/>
     </row>
     <row r="461" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="25"/>
-      <c r="E461" s="60"/>
+      <c r="E461" s="61"/>
     </row>
     <row r="462" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="25"/>
-      <c r="E462" s="60"/>
+      <c r="E462" s="61"/>
     </row>
     <row r="463" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="25"/>
-      <c r="E463" s="60"/>
+      <c r="E463" s="61"/>
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="25"/>
-      <c r="E464" s="60"/>
+      <c r="E464" s="61"/>
     </row>
     <row r="465" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="25"/>
-      <c r="E465" s="60"/>
+      <c r="E465" s="61"/>
     </row>
     <row r="466" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="25"/>
-      <c r="E466" s="60"/>
+      <c r="E466" s="61"/>
     </row>
     <row r="467" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="25"/>
-      <c r="E467" s="60"/>
+      <c r="E467" s="61"/>
     </row>
     <row r="468" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="25"/>
-      <c r="E468" s="60"/>
+      <c r="E468" s="61"/>
     </row>
     <row r="469" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="25"/>
-      <c r="E469" s="60"/>
+      <c r="E469" s="61"/>
     </row>
     <row r="470" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="25"/>
-      <c r="E470" s="60"/>
+      <c r="E470" s="61"/>
     </row>
     <row r="471" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="25"/>
-      <c r="E471" s="60"/>
+      <c r="E471" s="61"/>
     </row>
     <row r="472" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="25"/>
-      <c r="E472" s="60"/>
+      <c r="E472" s="61"/>
     </row>
     <row r="473" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="25"/>
-      <c r="E473" s="60"/>
+      <c r="E473" s="61"/>
     </row>
     <row r="474" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="25"/>
-      <c r="E474" s="60"/>
+      <c r="E474" s="61"/>
     </row>
     <row r="475" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="25"/>
-      <c r="E475" s="60"/>
+      <c r="E475" s="61"/>
     </row>
     <row r="476" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="25"/>
-      <c r="E476" s="60"/>
+      <c r="E476" s="61"/>
     </row>
     <row r="477" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="25"/>
-      <c r="E477" s="60"/>
+      <c r="E477" s="61"/>
     </row>
     <row r="478" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="25"/>
-      <c r="E478" s="60"/>
+      <c r="E478" s="61"/>
     </row>
     <row r="479" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="25"/>
-      <c r="E479" s="60"/>
+      <c r="E479" s="61"/>
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="25"/>
-      <c r="E480" s="60"/>
+      <c r="E480" s="61"/>
     </row>
     <row r="481" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="25"/>
-      <c r="E481" s="60"/>
+      <c r="E481" s="61"/>
     </row>
     <row r="482" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="25"/>
-      <c r="E482" s="60"/>
+      <c r="E482" s="61"/>
     </row>
     <row r="483" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="25"/>
-      <c r="E483" s="60"/>
+      <c r="E483" s="61"/>
     </row>
     <row r="484" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="25"/>
-      <c r="E484" s="60"/>
+      <c r="E484" s="61"/>
     </row>
     <row r="485" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="25"/>
-      <c r="E485" s="60"/>
+      <c r="E485" s="61"/>
     </row>
     <row r="486" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="25"/>
-      <c r="E486" s="60"/>
+      <c r="E486" s="61"/>
     </row>
     <row r="487" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="25"/>
-      <c r="E487" s="60"/>
+      <c r="E487" s="61"/>
     </row>
     <row r="488" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="25"/>
-      <c r="E488" s="60"/>
+      <c r="E488" s="61"/>
     </row>
     <row r="489" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="25"/>
-      <c r="E489" s="60"/>
+      <c r="E489" s="61"/>
     </row>
     <row r="490" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="25"/>
-      <c r="E490" s="60"/>
+      <c r="E490" s="61"/>
     </row>
     <row r="491" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="25"/>
-      <c r="E491" s="60"/>
+      <c r="E491" s="61"/>
     </row>
     <row r="492" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="25"/>
-      <c r="E492" s="60"/>
+      <c r="E492" s="61"/>
     </row>
     <row r="493" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="25"/>
-      <c r="E493" s="60"/>
+      <c r="E493" s="61"/>
     </row>
     <row r="494" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="25"/>
-      <c r="E494" s="60"/>
+      <c r="E494" s="61"/>
     </row>
     <row r="495" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="25"/>
-      <c r="E495" s="60"/>
+      <c r="E495" s="61"/>
     </row>
     <row r="496" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="25"/>
-      <c r="E496" s="60"/>
+      <c r="E496" s="61"/>
     </row>
     <row r="497" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="25"/>
-      <c r="E497" s="60"/>
+      <c r="E497" s="61"/>
     </row>
     <row r="498" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="25"/>
-      <c r="E498" s="60"/>
+      <c r="E498" s="61"/>
     </row>
     <row r="499" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="25"/>
-      <c r="E499" s="60"/>
+      <c r="E499" s="61"/>
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="25"/>
-      <c r="E500" s="60"/>
+      <c r="E500" s="61"/>
     </row>
     <row r="501" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="25"/>
-      <c r="E501" s="60"/>
+      <c r="E501" s="61"/>
     </row>
     <row r="502" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="25"/>
-      <c r="E502" s="60"/>
+      <c r="E502" s="61"/>
     </row>
     <row r="503" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="25"/>
-      <c r="E503" s="60"/>
+      <c r="E503" s="61"/>
     </row>
     <row r="504" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="25"/>
-      <c r="E504" s="60"/>
+      <c r="E504" s="61"/>
     </row>
     <row r="505" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="25"/>
-      <c r="E505" s="60"/>
+      <c r="E505" s="61"/>
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="25"/>
-      <c r="E506" s="60"/>
+      <c r="E506" s="61"/>
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="25"/>
-      <c r="E507" s="60"/>
+      <c r="E507" s="61"/>
     </row>
     <row r="508" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="25"/>
-      <c r="E508" s="60"/>
+      <c r="E508" s="61"/>
     </row>
     <row r="509" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="25"/>
-      <c r="E509" s="60"/>
+      <c r="E509" s="61"/>
     </row>
     <row r="510" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="25"/>
-      <c r="E510" s="60"/>
+      <c r="E510" s="61"/>
     </row>
     <row r="511" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="25"/>
-      <c r="E511" s="60"/>
+      <c r="E511" s="61"/>
     </row>
     <row r="512" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="25"/>
-      <c r="E512" s="60"/>
+      <c r="E512" s="61"/>
     </row>
     <row r="513" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="25"/>
-      <c r="E513" s="60"/>
+      <c r="E513" s="61"/>
     </row>
     <row r="514" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="25"/>
-      <c r="E514" s="60"/>
+      <c r="E514" s="61"/>
     </row>
     <row r="515" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="25"/>
-      <c r="E515" s="60"/>
+      <c r="E515" s="61"/>
     </row>
     <row r="516" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="25"/>
-      <c r="E516" s="60"/>
+      <c r="E516" s="61"/>
     </row>
     <row r="517" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="25"/>
-      <c r="E517" s="60"/>
+      <c r="E517" s="61"/>
     </row>
     <row r="518" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="25"/>
-      <c r="E518" s="60"/>
+      <c r="E518" s="61"/>
     </row>
     <row r="519" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="25"/>
-      <c r="E519" s="60"/>
+      <c r="E519" s="61"/>
     </row>
     <row r="520" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="25"/>
-      <c r="E520" s="60"/>
+      <c r="E520" s="61"/>
     </row>
     <row r="521" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="25"/>
-      <c r="E521" s="60"/>
+      <c r="E521" s="61"/>
     </row>
     <row r="522" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="25"/>
-      <c r="E522" s="60"/>
+      <c r="E522" s="61"/>
     </row>
     <row r="523" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="25"/>
-      <c r="E523" s="60"/>
+      <c r="E523" s="61"/>
     </row>
     <row r="524" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="25"/>
-      <c r="E524" s="60"/>
+      <c r="E524" s="61"/>
     </row>
     <row r="525" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="25"/>
-      <c r="E525" s="60"/>
+      <c r="E525" s="61"/>
     </row>
     <row r="526" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="25"/>
-      <c r="E526" s="60"/>
+      <c r="E526" s="61"/>
     </row>
     <row r="527" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="25"/>
-      <c r="E527" s="60"/>
+      <c r="E527" s="61"/>
     </row>
     <row r="528" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="25"/>
-      <c r="E528" s="60"/>
+      <c r="E528" s="61"/>
     </row>
     <row r="529" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="25"/>
-      <c r="E529" s="60"/>
+      <c r="E529" s="61"/>
     </row>
     <row r="530" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="25"/>
-      <c r="E530" s="60"/>
+      <c r="E530" s="61"/>
     </row>
     <row r="531" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="25"/>
-      <c r="E531" s="60"/>
+      <c r="E531" s="61"/>
     </row>
     <row r="532" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="25"/>
-      <c r="E532" s="60"/>
+      <c r="E532" s="61"/>
     </row>
     <row r="533" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="25"/>
-      <c r="E533" s="60"/>
+      <c r="E533" s="61"/>
     </row>
     <row r="534" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="25"/>
-      <c r="E534" s="60"/>
+      <c r="E534" s="61"/>
     </row>
     <row r="535" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="25"/>
-      <c r="E535" s="60"/>
+      <c r="E535" s="61"/>
     </row>
     <row r="536" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="25"/>
-      <c r="E536" s="60"/>
+      <c r="E536" s="61"/>
     </row>
     <row r="537" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="25"/>
-      <c r="E537" s="60"/>
+      <c r="E537" s="61"/>
     </row>
     <row r="538" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="25"/>
-      <c r="E538" s="60"/>
+      <c r="E538" s="61"/>
     </row>
     <row r="539" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="25"/>
-      <c r="E539" s="60"/>
+      <c r="E539" s="61"/>
     </row>
     <row r="540" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="25"/>
-      <c r="E540" s="60"/>
+      <c r="E540" s="61"/>
     </row>
     <row r="541" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="25"/>
-      <c r="E541" s="60"/>
+      <c r="E541" s="61"/>
     </row>
     <row r="542" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="25"/>
-      <c r="E542" s="60"/>
+      <c r="E542" s="61"/>
     </row>
     <row r="543" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="25"/>
-      <c r="E543" s="60"/>
+      <c r="E543" s="61"/>
     </row>
     <row r="544" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="25"/>
-      <c r="E544" s="60"/>
+      <c r="E544" s="61"/>
     </row>
     <row r="545" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="25"/>
-      <c r="E545" s="60"/>
+      <c r="E545" s="61"/>
     </row>
     <row r="546" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="25"/>
-      <c r="E546" s="60"/>
+      <c r="E546" s="61"/>
     </row>
     <row r="547" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="25"/>
-      <c r="E547" s="60"/>
+      <c r="E547" s="61"/>
     </row>
     <row r="548" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="25"/>
-      <c r="E548" s="60"/>
+      <c r="E548" s="61"/>
     </row>
     <row r="549" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="25"/>
-      <c r="E549" s="60"/>
+      <c r="E549" s="61"/>
     </row>
     <row r="550" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="25"/>
-      <c r="E550" s="60"/>
+      <c r="E550" s="61"/>
     </row>
     <row r="551" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="25"/>
-      <c r="E551" s="60"/>
+      <c r="E551" s="61"/>
     </row>
     <row r="552" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="25"/>
-      <c r="E552" s="60"/>
+      <c r="E552" s="61"/>
     </row>
     <row r="553" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="25"/>
-      <c r="E553" s="60"/>
+      <c r="E553" s="61"/>
     </row>
     <row r="554" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="25"/>
-      <c r="E554" s="60"/>
+      <c r="E554" s="61"/>
     </row>
     <row r="555" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="25"/>
-      <c r="E555" s="60"/>
+      <c r="E555" s="61"/>
     </row>
     <row r="556" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="25"/>
-      <c r="E556" s="60"/>
+      <c r="E556" s="61"/>
     </row>
     <row r="557" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="25"/>
-      <c r="E557" s="60"/>
+      <c r="E557" s="61"/>
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="25"/>
-      <c r="E558" s="60"/>
+      <c r="E558" s="61"/>
     </row>
     <row r="559" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="25"/>
-      <c r="E559" s="60"/>
+      <c r="E559" s="61"/>
     </row>
     <row r="560" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="25"/>
-      <c r="E560" s="60"/>
+      <c r="E560" s="61"/>
     </row>
     <row r="561" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="25"/>
-      <c r="E561" s="60"/>
+      <c r="E561" s="61"/>
     </row>
     <row r="562" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="25"/>
-      <c r="E562" s="60"/>
+      <c r="E562" s="61"/>
     </row>
     <row r="563" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="25"/>
-      <c r="E563" s="60"/>
+      <c r="E563" s="61"/>
     </row>
     <row r="564" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="25"/>
-      <c r="E564" s="60"/>
+      <c r="E564" s="61"/>
     </row>
     <row r="565" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="25"/>
-      <c r="E565" s="60"/>
+      <c r="E565" s="61"/>
     </row>
     <row r="566" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="25"/>
-      <c r="E566" s="60"/>
+      <c r="E566" s="61"/>
     </row>
     <row r="567" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="25"/>
-      <c r="E567" s="60"/>
+      <c r="E567" s="61"/>
     </row>
     <row r="568" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="25"/>
-      <c r="E568" s="60"/>
+      <c r="E568" s="61"/>
     </row>
     <row r="569" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="25"/>
-      <c r="E569" s="60"/>
+      <c r="E569" s="61"/>
     </row>
     <row r="570" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="25"/>
-      <c r="E570" s="60"/>
+      <c r="E570" s="61"/>
     </row>
     <row r="571" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="25"/>
-      <c r="E571" s="60"/>
+      <c r="E571" s="61"/>
     </row>
     <row r="572" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="25"/>
-      <c r="E572" s="60"/>
+      <c r="E572" s="61"/>
     </row>
     <row r="573" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="25"/>
-      <c r="E573" s="60"/>
+      <c r="E573" s="61"/>
     </row>
     <row r="574" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="25"/>
-      <c r="E574" s="60"/>
+      <c r="E574" s="61"/>
     </row>
     <row r="575" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="25"/>
-      <c r="E575" s="60"/>
+      <c r="E575" s="61"/>
     </row>
     <row r="576" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="25"/>
-      <c r="E576" s="60"/>
+      <c r="E576" s="61"/>
     </row>
     <row r="577" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="25"/>
-      <c r="E577" s="60"/>
+      <c r="E577" s="61"/>
     </row>
     <row r="578" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="25"/>
-      <c r="E578" s="60"/>
+      <c r="E578" s="61"/>
     </row>
     <row r="579" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="25"/>
-      <c r="E579" s="60"/>
+      <c r="E579" s="61"/>
     </row>
     <row r="580" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="25"/>
-      <c r="E580" s="60"/>
+      <c r="E580" s="61"/>
     </row>
     <row r="581" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="25"/>
-      <c r="E581" s="60"/>
+      <c r="E581" s="61"/>
     </row>
     <row r="582" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="25"/>
-      <c r="E582" s="60"/>
+      <c r="E582" s="61"/>
     </row>
     <row r="583" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="25"/>
-      <c r="E583" s="60"/>
+      <c r="E583" s="61"/>
     </row>
     <row r="584" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="25"/>
-      <c r="E584" s="60"/>
+      <c r="E584" s="61"/>
     </row>
     <row r="585" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="25"/>
-      <c r="E585" s="60"/>
+      <c r="E585" s="61"/>
     </row>
     <row r="586" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="25"/>
-      <c r="E586" s="60"/>
+      <c r="E586" s="61"/>
     </row>
     <row r="587" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="25"/>
-      <c r="E587" s="60"/>
+      <c r="E587" s="61"/>
     </row>
     <row r="588" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="25"/>
-      <c r="E588" s="60"/>
+      <c r="E588" s="61"/>
     </row>
     <row r="589" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="25"/>
-      <c r="E589" s="60"/>
+      <c r="E589" s="61"/>
     </row>
     <row r="590" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="25"/>
-      <c r="E590" s="60"/>
+      <c r="E590" s="61"/>
     </row>
     <row r="591" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="25"/>
-      <c r="E591" s="60"/>
+      <c r="E591" s="61"/>
     </row>
     <row r="592" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="25"/>
-      <c r="E592" s="60"/>
+      <c r="E592" s="61"/>
     </row>
     <row r="593" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="25"/>
-      <c r="E593" s="60"/>
+      <c r="E593" s="61"/>
     </row>
     <row r="594" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="25"/>
-      <c r="E594" s="60"/>
+      <c r="E594" s="61"/>
     </row>
     <row r="595" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="25"/>
-      <c r="E595" s="60"/>
+      <c r="E595" s="61"/>
     </row>
     <row r="596" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="25"/>
-      <c r="E596" s="60"/>
+      <c r="E596" s="61"/>
     </row>
     <row r="597" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="25"/>
-      <c r="E597" s="60"/>
+      <c r="E597" s="61"/>
     </row>
     <row r="598" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="25"/>
-      <c r="E598" s="60"/>
+      <c r="E598" s="61"/>
     </row>
     <row r="599" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="25"/>
-      <c r="E599" s="60"/>
+      <c r="E599" s="61"/>
     </row>
     <row r="600" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="25"/>
-      <c r="E600" s="60"/>
+      <c r="E600" s="61"/>
     </row>
     <row r="601" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="25"/>
-      <c r="E601" s="60"/>
+      <c r="E601" s="61"/>
     </row>
     <row r="602" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="25"/>
-      <c r="E602" s="60"/>
+      <c r="E602" s="61"/>
     </row>
     <row r="603" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="25"/>
-      <c r="E603" s="60"/>
+      <c r="E603" s="61"/>
     </row>
     <row r="604" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="25"/>
-      <c r="E604" s="60"/>
+      <c r="E604" s="61"/>
     </row>
     <row r="605" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="25"/>
-      <c r="E605" s="60"/>
+      <c r="E605" s="61"/>
     </row>
     <row r="606" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="25"/>
-      <c r="E606" s="60"/>
+      <c r="E606" s="61"/>
     </row>
     <row r="607" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="25"/>
-      <c r="E607" s="60"/>
+      <c r="E607" s="61"/>
     </row>
     <row r="608" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="25"/>
-      <c r="E608" s="60"/>
+      <c r="E608" s="61"/>
     </row>
     <row r="609" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="25"/>
-      <c r="E609" s="60"/>
+      <c r="E609" s="61"/>
     </row>
     <row r="610" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="25"/>
-      <c r="E610" s="60"/>
+      <c r="E610" s="61"/>
     </row>
     <row r="611" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="25"/>
-      <c r="E611" s="60"/>
+      <c r="E611" s="61"/>
     </row>
     <row r="612" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="25"/>
-      <c r="E612" s="60"/>
+      <c r="E612" s="61"/>
     </row>
     <row r="613" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="25"/>
-      <c r="E613" s="60"/>
+      <c r="E613" s="61"/>
     </row>
     <row r="614" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="25"/>
-      <c r="E614" s="60"/>
+      <c r="E614" s="61"/>
     </row>
     <row r="615" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="25"/>
-      <c r="E615" s="60"/>
+      <c r="E615" s="61"/>
     </row>
     <row r="616" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="25"/>
-      <c r="E616" s="60"/>
+      <c r="E616" s="61"/>
     </row>
     <row r="617" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="25"/>
-      <c r="E617" s="60"/>
+      <c r="E617" s="61"/>
     </row>
     <row r="618" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="25"/>
-      <c r="E618" s="60"/>
+      <c r="E618" s="61"/>
     </row>
     <row r="619" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="25"/>
-      <c r="E619" s="60"/>
+      <c r="E619" s="61"/>
     </row>
     <row r="620" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="25"/>
-      <c r="E620" s="60"/>
+      <c r="E620" s="61"/>
     </row>
     <row r="621" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="25"/>
-      <c r="E621" s="60"/>
+      <c r="E621" s="61"/>
     </row>
     <row r="622" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="25"/>
-      <c r="E622" s="60"/>
+      <c r="E622" s="61"/>
     </row>
     <row r="623" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="25"/>
-      <c r="E623" s="60"/>
+      <c r="E623" s="61"/>
     </row>
     <row r="624" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="25"/>
-      <c r="E624" s="60"/>
+      <c r="E624" s="61"/>
     </row>
     <row r="625" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="25"/>
-      <c r="E625" s="60"/>
+      <c r="E625" s="61"/>
     </row>
     <row r="626" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="25"/>
-      <c r="E626" s="60"/>
+      <c r="E626" s="61"/>
     </row>
     <row r="627" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="25"/>
-      <c r="E627" s="60"/>
+      <c r="E627" s="61"/>
     </row>
     <row r="628" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="25"/>
-      <c r="E628" s="60"/>
+      <c r="E628" s="61"/>
     </row>
     <row r="629" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="25"/>
-      <c r="E629" s="60"/>
+      <c r="E629" s="61"/>
     </row>
     <row r="630" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="25"/>
-      <c r="E630" s="60"/>
+      <c r="E630" s="61"/>
     </row>
     <row r="631" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="25"/>
-      <c r="E631" s="60"/>
+      <c r="E631" s="61"/>
     </row>
     <row r="632" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="25"/>
-      <c r="E632" s="60"/>
+      <c r="E632" s="61"/>
     </row>
     <row r="633" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="25"/>
-      <c r="E633" s="60"/>
+      <c r="E633" s="61"/>
     </row>
     <row r="634" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="25"/>
-      <c r="E634" s="60"/>
+      <c r="E634" s="61"/>
     </row>
     <row r="635" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="25"/>
-      <c r="E635" s="60"/>
+      <c r="E635" s="61"/>
     </row>
     <row r="636" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="25"/>
-      <c r="E636" s="60"/>
+      <c r="E636" s="61"/>
     </row>
     <row r="637" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="25"/>
-      <c r="E637" s="60"/>
+      <c r="E637" s="61"/>
     </row>
     <row r="638" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="25"/>
-      <c r="E638" s="60"/>
+      <c r="E638" s="61"/>
     </row>
     <row r="639" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="25"/>
-      <c r="E639" s="60"/>
+      <c r="E639" s="61"/>
     </row>
     <row r="640" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="25"/>
-      <c r="E640" s="60"/>
+      <c r="E640" s="61"/>
     </row>
     <row r="641" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="25"/>
-      <c r="E641" s="60"/>
+      <c r="E641" s="61"/>
     </row>
     <row r="642" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="25"/>
-      <c r="E642" s="60"/>
+      <c r="E642" s="61"/>
     </row>
     <row r="643" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="25"/>
-      <c r="E643" s="60"/>
+      <c r="E643" s="61"/>
     </row>
     <row r="644" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="25"/>
-      <c r="E644" s="60"/>
+      <c r="E644" s="61"/>
     </row>
     <row r="645" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="25"/>
-      <c r="E645" s="60"/>
+      <c r="E645" s="61"/>
     </row>
     <row r="646" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="25"/>
-      <c r="E646" s="60"/>
+      <c r="E646" s="61"/>
     </row>
     <row r="647" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="25"/>
-      <c r="E647" s="60"/>
+      <c r="E647" s="61"/>
     </row>
     <row r="648" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="25"/>
-      <c r="E648" s="60"/>
+      <c r="E648" s="61"/>
     </row>
     <row r="649" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="25"/>
-      <c r="E649" s="60"/>
+      <c r="E649" s="61"/>
     </row>
     <row r="650" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="25"/>
-      <c r="E650" s="60"/>
+      <c r="E650" s="61"/>
     </row>
     <row r="651" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="25"/>
-      <c r="E651" s="60"/>
+      <c r="E651" s="61"/>
     </row>
     <row r="652" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="25"/>
-      <c r="E652" s="60"/>
+      <c r="E652" s="61"/>
     </row>
     <row r="653" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="25"/>
-      <c r="E653" s="60"/>
+      <c r="E653" s="61"/>
     </row>
     <row r="654" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="25"/>
-      <c r="E654" s="60"/>
+      <c r="E654" s="61"/>
     </row>
     <row r="655" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="25"/>
-      <c r="E655" s="60"/>
+      <c r="E655" s="61"/>
     </row>
     <row r="656" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="25"/>
-      <c r="E656" s="60"/>
+      <c r="E656" s="61"/>
     </row>
     <row r="657" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="25"/>
-      <c r="E657" s="60"/>
+      <c r="E657" s="61"/>
     </row>
     <row r="658" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="25"/>
-      <c r="E658" s="60"/>
+      <c r="E658" s="61"/>
     </row>
     <row r="659" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="25"/>
-      <c r="E659" s="60"/>
+      <c r="E659" s="61"/>
     </row>
     <row r="660" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="25"/>
-      <c r="E660" s="60"/>
+      <c r="E660" s="61"/>
     </row>
     <row r="661" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="25"/>
-      <c r="E661" s="60"/>
+      <c r="E661" s="61"/>
     </row>
     <row r="662" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="25"/>
-      <c r="E662" s="60"/>
+      <c r="E662" s="61"/>
     </row>
     <row r="663" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="25"/>
-      <c r="E663" s="60"/>
+      <c r="E663" s="61"/>
     </row>
     <row r="664" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="25"/>
-      <c r="E664" s="60"/>
+      <c r="E664" s="61"/>
     </row>
     <row r="665" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="25"/>
-      <c r="E665" s="60"/>
+      <c r="E665" s="61"/>
     </row>
     <row r="666" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="25"/>
-      <c r="E666" s="60"/>
+      <c r="E666" s="61"/>
     </row>
     <row r="667" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="25"/>
-      <c r="E667" s="60"/>
+      <c r="E667" s="61"/>
     </row>
     <row r="668" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="25"/>
-      <c r="E668" s="60"/>
+      <c r="E668" s="61"/>
     </row>
     <row r="669" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="25"/>
-      <c r="E669" s="60"/>
+      <c r="E669" s="61"/>
     </row>
     <row r="670" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="25"/>
-      <c r="E670" s="60"/>
+      <c r="E670" s="61"/>
     </row>
     <row r="671" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="25"/>
-      <c r="E671" s="60"/>
+      <c r="E671" s="61"/>
     </row>
     <row r="672" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="25"/>
-      <c r="E672" s="60"/>
+      <c r="E672" s="61"/>
     </row>
     <row r="673" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="25"/>
-      <c r="E673" s="60"/>
+      <c r="E673" s="61"/>
     </row>
     <row r="674" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="25"/>
-      <c r="E674" s="60"/>
+      <c r="E674" s="61"/>
     </row>
     <row r="675" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="25"/>
-      <c r="E675" s="60"/>
+      <c r="E675" s="61"/>
     </row>
     <row r="676" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="25"/>
-      <c r="E676" s="60"/>
+      <c r="E676" s="61"/>
     </row>
     <row r="677" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="25"/>
-      <c r="E677" s="60"/>
+      <c r="E677" s="61"/>
     </row>
     <row r="678" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="25"/>
-      <c r="E678" s="60"/>
+      <c r="E678" s="61"/>
     </row>
     <row r="679" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="25"/>
-      <c r="E679" s="60"/>
+      <c r="E679" s="61"/>
     </row>
     <row r="680" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="25"/>
-      <c r="E680" s="60"/>
+      <c r="E680" s="61"/>
     </row>
     <row r="681" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="25"/>
-      <c r="E681" s="60"/>
+      <c r="E681" s="61"/>
     </row>
     <row r="682" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="25"/>
-      <c r="E682" s="60"/>
+      <c r="E682" s="61"/>
     </row>
     <row r="683" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="25"/>
-      <c r="E683" s="60"/>
+      <c r="E683" s="61"/>
     </row>
     <row r="684" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="25"/>
-      <c r="E684" s="60"/>
+      <c r="E684" s="61"/>
     </row>
     <row r="685" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="25"/>
-      <c r="E685" s="60"/>
+      <c r="E685" s="61"/>
     </row>
     <row r="686" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="25"/>
-      <c r="E686" s="60"/>
+      <c r="E686" s="61"/>
     </row>
     <row r="687" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="25"/>
-      <c r="E687" s="60"/>
+      <c r="E687" s="61"/>
     </row>
     <row r="688" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="25"/>
-      <c r="E688" s="60"/>
+      <c r="E688" s="61"/>
     </row>
     <row r="689" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="25"/>
-      <c r="E689" s="60"/>
+      <c r="E689" s="61"/>
     </row>
     <row r="690" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="25"/>
-      <c r="E690" s="60"/>
+      <c r="E690" s="61"/>
     </row>
     <row r="691" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="25"/>
-      <c r="E691" s="60"/>
+      <c r="E691" s="61"/>
     </row>
     <row r="692" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="25"/>
-      <c r="E692" s="60"/>
+      <c r="E692" s="61"/>
     </row>
     <row r="693" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="25"/>
-      <c r="E693" s="60"/>
+      <c r="E693" s="61"/>
     </row>
     <row r="694" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="25"/>
-      <c r="E694" s="60"/>
+      <c r="E694" s="61"/>
     </row>
     <row r="695" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="25"/>
-      <c r="E695" s="60"/>
+      <c r="E695" s="61"/>
     </row>
     <row r="696" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="25"/>
-      <c r="E696" s="60"/>
+      <c r="E696" s="61"/>
     </row>
     <row r="697" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="25"/>
-      <c r="E697" s="60"/>
+      <c r="E697" s="61"/>
     </row>
     <row r="698" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="25"/>
-      <c r="E698" s="60"/>
+      <c r="E698" s="61"/>
     </row>
     <row r="699" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="25"/>
-      <c r="E699" s="60"/>
+      <c r="E699" s="61"/>
     </row>
     <row r="700" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="25"/>
-      <c r="E700" s="60"/>
+      <c r="E700" s="61"/>
     </row>
     <row r="701" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="25"/>
-      <c r="E701" s="60"/>
+      <c r="E701" s="61"/>
     </row>
     <row r="702" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="25"/>
-      <c r="E702" s="60"/>
+      <c r="E702" s="61"/>
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="25"/>
-      <c r="E703" s="60"/>
+      <c r="E703" s="61"/>
     </row>
     <row r="704" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="25"/>
-      <c r="E704" s="60"/>
+      <c r="E704" s="61"/>
     </row>
     <row r="705" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="25"/>
-      <c r="E705" s="60"/>
+      <c r="E705" s="61"/>
     </row>
     <row r="706" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="25"/>
-      <c r="E706" s="60"/>
+      <c r="E706" s="61"/>
     </row>
     <row r="707" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="25"/>
-      <c r="E707" s="60"/>
+      <c r="E707" s="61"/>
     </row>
     <row r="708" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="25"/>
-      <c r="E708" s="60"/>
+      <c r="E708" s="61"/>
     </row>
     <row r="709" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="25"/>
-      <c r="E709" s="60"/>
+      <c r="E709" s="61"/>
     </row>
     <row r="710" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="25"/>
-      <c r="E710" s="60"/>
+      <c r="E710" s="61"/>
     </row>
     <row r="711" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="25"/>
-      <c r="E711" s="60"/>
+      <c r="E711" s="61"/>
     </row>
     <row r="712" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="25"/>
-      <c r="E712" s="60"/>
+      <c r="E712" s="61"/>
     </row>
     <row r="713" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="25"/>
-      <c r="E713" s="60"/>
+      <c r="E713" s="61"/>
     </row>
     <row r="714" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="25"/>
-      <c r="E714" s="60"/>
+      <c r="E714" s="61"/>
     </row>
     <row r="715" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="25"/>
-      <c r="E715" s="60"/>
+      <c r="E715" s="61"/>
     </row>
     <row r="716" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="25"/>
-      <c r="E716" s="60"/>
+      <c r="E716" s="61"/>
     </row>
     <row r="717" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="25"/>
-      <c r="E717" s="60"/>
+      <c r="E717" s="61"/>
     </row>
     <row r="718" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="25"/>
-      <c r="E718" s="60"/>
+      <c r="E718" s="61"/>
     </row>
     <row r="719" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="25"/>
-      <c r="E719" s="60"/>
+      <c r="E719" s="61"/>
     </row>
     <row r="720" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="25"/>
-      <c r="E720" s="60"/>
+      <c r="E720" s="61"/>
     </row>
     <row r="721" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="25"/>
-      <c r="E721" s="60"/>
+      <c r="E721" s="61"/>
     </row>
     <row r="722" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="25"/>
-      <c r="E722" s="60"/>
+      <c r="E722" s="61"/>
     </row>
     <row r="723" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="25"/>
-      <c r="E723" s="60"/>
+      <c r="E723" s="61"/>
     </row>
     <row r="724" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="25"/>
-      <c r="E724" s="60"/>
+      <c r="E724" s="61"/>
     </row>
     <row r="725" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="25"/>
-      <c r="E725" s="60"/>
+      <c r="E725" s="61"/>
     </row>
     <row r="726" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="25"/>
-      <c r="E726" s="60"/>
+      <c r="E726" s="61"/>
     </row>
     <row r="727" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="25"/>
-      <c r="E727" s="60"/>
+      <c r="E727" s="61"/>
     </row>
     <row r="728" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="25"/>
-      <c r="E728" s="60"/>
+      <c r="E728" s="61"/>
     </row>
     <row r="729" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="25"/>
-      <c r="E729" s="60"/>
+      <c r="E729" s="61"/>
     </row>
     <row r="730" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="25"/>
-      <c r="E730" s="60"/>
+      <c r="E730" s="61"/>
     </row>
     <row r="731" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="25"/>
-      <c r="E731" s="60"/>
+      <c r="E731" s="61"/>
     </row>
     <row r="732" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="25"/>
-      <c r="E732" s="60"/>
+      <c r="E732" s="61"/>
     </row>
     <row r="733" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="25"/>
-      <c r="E733" s="60"/>
+      <c r="E733" s="61"/>
     </row>
     <row r="734" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="25"/>
-      <c r="E734" s="60"/>
+      <c r="E734" s="61"/>
     </row>
     <row r="735" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="25"/>
-      <c r="E735" s="60"/>
+      <c r="E735" s="61"/>
     </row>
     <row r="736" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="25"/>
-      <c r="E736" s="60"/>
+      <c r="E736" s="61"/>
     </row>
     <row r="737" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="25"/>
-      <c r="E737" s="60"/>
+      <c r="E737" s="61"/>
     </row>
     <row r="738" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="25"/>
-      <c r="E738" s="60"/>
+      <c r="E738" s="61"/>
     </row>
     <row r="739" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="25"/>
-      <c r="E739" s="60"/>
+      <c r="E739" s="61"/>
     </row>
     <row r="740" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="25"/>
-      <c r="E740" s="60"/>
+      <c r="E740" s="61"/>
     </row>
     <row r="741" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="25"/>
-      <c r="E741" s="60"/>
+      <c r="E741" s="61"/>
     </row>
     <row r="742" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="25"/>
-      <c r="E742" s="60"/>
+      <c r="E742" s="61"/>
     </row>
     <row r="743" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="25"/>
-      <c r="E743" s="60"/>
+      <c r="E743" s="61"/>
     </row>
     <row r="744" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="25"/>
-      <c r="E744" s="60"/>
+      <c r="E744" s="61"/>
     </row>
     <row r="745" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="25"/>
-      <c r="E745" s="60"/>
+      <c r="E745" s="61"/>
     </row>
     <row r="746" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="25"/>
-      <c r="E746" s="60"/>
+      <c r="E746" s="61"/>
     </row>
     <row r="747" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="25"/>
-      <c r="E747" s="60"/>
+      <c r="E747" s="61"/>
     </row>
     <row r="748" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="25"/>
-      <c r="E748" s="60"/>
+      <c r="E748" s="61"/>
     </row>
     <row r="749" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="25"/>
-      <c r="E749" s="60"/>
+      <c r="E749" s="61"/>
     </row>
     <row r="750" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="25"/>
-      <c r="E750" s="60"/>
+      <c r="E750" s="61"/>
     </row>
     <row r="751" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="25"/>
-      <c r="E751" s="60"/>
+      <c r="E751" s="61"/>
     </row>
     <row r="752" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="25"/>
-      <c r="E752" s="60"/>
+      <c r="E752" s="61"/>
     </row>
     <row r="753" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="25"/>
-      <c r="E753" s="60"/>
+      <c r="E753" s="61"/>
     </row>
     <row r="754" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="25"/>
-      <c r="E754" s="60"/>
+      <c r="E754" s="61"/>
     </row>
     <row r="755" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="25"/>
-      <c r="E755" s="60"/>
+      <c r="E755" s="61"/>
     </row>
     <row r="756" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="25"/>
-      <c r="E756" s="60"/>
+      <c r="E756" s="61"/>
     </row>
     <row r="757" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="25"/>
-      <c r="E757" s="60"/>
+      <c r="E757" s="61"/>
     </row>
     <row r="758" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="25"/>
-      <c r="E758" s="60"/>
+      <c r="E758" s="61"/>
     </row>
     <row r="759" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="25"/>
-      <c r="E759" s="60"/>
+      <c r="E759" s="61"/>
     </row>
     <row r="760" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="25"/>
-      <c r="E760" s="60"/>
+      <c r="E760" s="61"/>
     </row>
     <row r="761" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="25"/>
-      <c r="E761" s="60"/>
+      <c r="E761" s="61"/>
     </row>
     <row r="762" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="25"/>
-      <c r="E762" s="60"/>
+      <c r="E762" s="61"/>
     </row>
     <row r="763" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="25"/>
-      <c r="E763" s="60"/>
+      <c r="E763" s="61"/>
     </row>
     <row r="764" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="25"/>
-      <c r="E764" s="60"/>
+      <c r="E764" s="61"/>
     </row>
     <row r="765" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="25"/>
-      <c r="E765" s="60"/>
+      <c r="E765" s="61"/>
     </row>
     <row r="766" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="25"/>
-      <c r="E766" s="60"/>
+      <c r="E766" s="61"/>
     </row>
     <row r="767" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="25"/>
-      <c r="E767" s="60"/>
+      <c r="E767" s="61"/>
     </row>
     <row r="768" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="25"/>
-      <c r="E768" s="60"/>
+      <c r="E768" s="61"/>
     </row>
     <row r="769" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="25"/>
-      <c r="E769" s="60"/>
+      <c r="E769" s="61"/>
     </row>
     <row r="770" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="25"/>
-      <c r="E770" s="60"/>
+      <c r="E770" s="61"/>
     </row>
     <row r="771" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="25"/>
-      <c r="E771" s="60"/>
+      <c r="E771" s="61"/>
     </row>
     <row r="772" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="25"/>
-      <c r="E772" s="60"/>
+      <c r="E772" s="61"/>
     </row>
     <row r="773" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="25"/>
-      <c r="E773" s="60"/>
+      <c r="E773" s="61"/>
     </row>
     <row r="774" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="25"/>
-      <c r="E774" s="60"/>
+      <c r="E774" s="61"/>
     </row>
     <row r="775" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="25"/>
-      <c r="E775" s="60"/>
+      <c r="E775" s="61"/>
     </row>
     <row r="776" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="25"/>
-      <c r="E776" s="60"/>
+      <c r="E776" s="61"/>
     </row>
     <row r="777" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="25"/>
-      <c r="E777" s="60"/>
+      <c r="E777" s="61"/>
     </row>
     <row r="778" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="25"/>
-      <c r="E778" s="60"/>
+      <c r="E778" s="61"/>
     </row>
     <row r="779" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="25"/>
-      <c r="E779" s="60"/>
+      <c r="E779" s="61"/>
     </row>
     <row r="780" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="25"/>
-      <c r="E780" s="60"/>
+      <c r="E780" s="61"/>
     </row>
     <row r="781" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="25"/>
-      <c r="E781" s="60"/>
+      <c r="E781" s="61"/>
     </row>
     <row r="782" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="25"/>
-      <c r="E782" s="60"/>
+      <c r="E782" s="61"/>
     </row>
     <row r="783" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="25"/>
-      <c r="E783" s="60"/>
+      <c r="E783" s="61"/>
     </row>
     <row r="784" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="25"/>
-      <c r="E784" s="60"/>
+      <c r="E784" s="61"/>
     </row>
     <row r="785" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="25"/>
-      <c r="E785" s="60"/>
+      <c r="E785" s="61"/>
     </row>
     <row r="786" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="25"/>
-      <c r="E786" s="60"/>
+      <c r="E786" s="61"/>
     </row>
     <row r="787" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="25"/>
-      <c r="E787" s="60"/>
+      <c r="E787" s="61"/>
     </row>
     <row r="788" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="25"/>
-      <c r="E788" s="60"/>
+      <c r="E788" s="61"/>
     </row>
     <row r="789" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="25"/>
-      <c r="E789" s="60"/>
+      <c r="E789" s="61"/>
     </row>
     <row r="790" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="25"/>
-      <c r="E790" s="60"/>
+      <c r="E790" s="61"/>
     </row>
     <row r="791" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="25"/>
-      <c r="E791" s="60"/>
+      <c r="E791" s="61"/>
     </row>
     <row r="792" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="25"/>
-      <c r="E792" s="60"/>
+      <c r="E792" s="61"/>
     </row>
     <row r="793" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="25"/>
-      <c r="E793" s="60"/>
+      <c r="E793" s="61"/>
     </row>
     <row r="794" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="25"/>
-      <c r="E794" s="60"/>
+      <c r="E794" s="61"/>
     </row>
     <row r="795" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="25"/>
-      <c r="E795" s="60"/>
+      <c r="E795" s="61"/>
     </row>
     <row r="796" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="25"/>
-      <c r="E796" s="60"/>
+      <c r="E796" s="61"/>
     </row>
     <row r="797" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="25"/>
-      <c r="E797" s="60"/>
+      <c r="E797" s="61"/>
     </row>
     <row r="798" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="25"/>
-      <c r="E798" s="60"/>
+      <c r="E798" s="61"/>
     </row>
     <row r="799" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="25"/>
-      <c r="E799" s="60"/>
+      <c r="E799" s="61"/>
     </row>
     <row r="800" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="25"/>
-      <c r="E800" s="60"/>
+      <c r="E800" s="61"/>
     </row>
     <row r="801" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="25"/>
-      <c r="E801" s="60"/>
+      <c r="E801" s="61"/>
     </row>
     <row r="802" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="25"/>
-      <c r="E802" s="60"/>
+      <c r="E802" s="61"/>
     </row>
     <row r="803" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="25"/>
-      <c r="E803" s="60"/>
+      <c r="E803" s="61"/>
     </row>
     <row r="804" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="25"/>
-      <c r="E804" s="60"/>
+      <c r="E804" s="61"/>
     </row>
     <row r="805" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="25"/>
-      <c r="E805" s="60"/>
+      <c r="E805" s="61"/>
     </row>
     <row r="806" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="25"/>
-      <c r="E806" s="60"/>
+      <c r="E806" s="61"/>
     </row>
     <row r="807" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="25"/>
-      <c r="E807" s="60"/>
+      <c r="E807" s="61"/>
     </row>
     <row r="808" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="25"/>
-      <c r="E808" s="60"/>
+      <c r="E808" s="61"/>
     </row>
     <row r="809" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="25"/>
-      <c r="E809" s="60"/>
+      <c r="E809" s="61"/>
     </row>
     <row r="810" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="25"/>
-      <c r="E810" s="60"/>
+      <c r="E810" s="61"/>
     </row>
     <row r="811" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="25"/>
-      <c r="E811" s="60"/>
+      <c r="E811" s="61"/>
     </row>
     <row r="812" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="25"/>
-      <c r="E812" s="60"/>
+      <c r="E812" s="61"/>
     </row>
     <row r="813" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="25"/>
-      <c r="E813" s="60"/>
+      <c r="E813" s="61"/>
     </row>
     <row r="814" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="25"/>
-      <c r="E814" s="60"/>
+      <c r="E814" s="61"/>
     </row>
     <row r="815" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="25"/>
-      <c r="E815" s="60"/>
+      <c r="E815" s="61"/>
     </row>
     <row r="816" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="25"/>
-      <c r="E816" s="60"/>
+      <c r="E816" s="61"/>
     </row>
     <row r="817" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="25"/>
-      <c r="E817" s="60"/>
+      <c r="E817" s="61"/>
     </row>
     <row r="818" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="25"/>
-      <c r="E818" s="60"/>
+      <c r="E818" s="61"/>
     </row>
     <row r="819" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="25"/>
-      <c r="E819" s="60"/>
+      <c r="E819" s="61"/>
     </row>
     <row r="820" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="25"/>
-      <c r="E820" s="60"/>
+      <c r="E820" s="61"/>
     </row>
     <row r="821" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="25"/>
-      <c r="E821" s="60"/>
+      <c r="E821" s="61"/>
     </row>
     <row r="822" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="25"/>
-      <c r="E822" s="60"/>
+      <c r="E822" s="61"/>
     </row>
     <row r="823" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="25"/>
-      <c r="E823" s="60"/>
+      <c r="E823" s="61"/>
     </row>
     <row r="824" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="25"/>
-      <c r="E824" s="60"/>
+      <c r="E824" s="61"/>
     </row>
     <row r="825" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="25"/>
-      <c r="E825" s="60"/>
+      <c r="E825" s="61"/>
     </row>
     <row r="826" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="25"/>
-      <c r="E826" s="60"/>
+      <c r="E826" s="61"/>
     </row>
     <row r="827" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="25"/>
-      <c r="E827" s="60"/>
+      <c r="E827" s="61"/>
     </row>
     <row r="828" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="25"/>
-      <c r="E828" s="60"/>
+      <c r="E828" s="61"/>
     </row>
     <row r="829" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="25"/>
-      <c r="E829" s="60"/>
+      <c r="E829" s="61"/>
     </row>
     <row r="830" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="25"/>
-      <c r="E830" s="60"/>
+      <c r="E830" s="61"/>
     </row>
     <row r="831" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="25"/>
-      <c r="E831" s="60"/>
+      <c r="E831" s="61"/>
     </row>
     <row r="832" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="25"/>
-      <c r="E832" s="60"/>
+      <c r="E832" s="61"/>
     </row>
     <row r="833" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="25"/>
-      <c r="E833" s="60"/>
+      <c r="E833" s="61"/>
     </row>
     <row r="834" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="25"/>
-      <c r="E834" s="60"/>
+      <c r="E834" s="61"/>
     </row>
     <row r="835" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="25"/>
-      <c r="E835" s="60"/>
+      <c r="E835" s="61"/>
     </row>
     <row r="836" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="25"/>
-      <c r="E836" s="60"/>
+      <c r="E836" s="61"/>
     </row>
     <row r="837" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="25"/>
-      <c r="E837" s="60"/>
+      <c r="E837" s="61"/>
     </row>
     <row r="838" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="25"/>
-      <c r="E838" s="60"/>
+      <c r="E838" s="61"/>
     </row>
     <row r="839" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="25"/>
-      <c r="E839" s="60"/>
+      <c r="E839" s="61"/>
     </row>
     <row r="840" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="25"/>
-      <c r="E840" s="60"/>
+      <c r="E840" s="61"/>
     </row>
     <row r="841" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="25"/>
-      <c r="E841" s="60"/>
+      <c r="E841" s="61"/>
     </row>
     <row r="842" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="25"/>
-      <c r="E842" s="60"/>
+      <c r="E842" s="61"/>
     </row>
     <row r="843" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="25"/>
-      <c r="E843" s="60"/>
+      <c r="E843" s="61"/>
     </row>
     <row r="844" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="25"/>
-      <c r="E844" s="60"/>
+      <c r="E844" s="61"/>
     </row>
     <row r="845" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="25"/>
-      <c r="E845" s="60"/>
+      <c r="E845" s="61"/>
     </row>
     <row r="846" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="25"/>
-      <c r="E846" s="60"/>
+      <c r="E846" s="61"/>
     </row>
     <row r="847" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="25"/>
-      <c r="E847" s="60"/>
+      <c r="E847" s="61"/>
     </row>
     <row r="848" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="25"/>
-      <c r="E848" s="60"/>
+      <c r="E848" s="61"/>
     </row>
     <row r="849" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="25"/>
-      <c r="E849" s="60"/>
+      <c r="E849" s="61"/>
     </row>
     <row r="850" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="25"/>
-      <c r="E850" s="60"/>
+      <c r="E850" s="61"/>
     </row>
     <row r="851" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="25"/>
-      <c r="E851" s="60"/>
+      <c r="E851" s="61"/>
     </row>
     <row r="852" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="25"/>
-      <c r="E852" s="60"/>
+      <c r="E852" s="61"/>
     </row>
     <row r="853" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="25"/>
-      <c r="E853" s="60"/>
+      <c r="E853" s="61"/>
     </row>
     <row r="854" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="25"/>
-      <c r="E854" s="60"/>
+      <c r="E854" s="61"/>
     </row>
     <row r="855" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="25"/>
-      <c r="E855" s="60"/>
+      <c r="E855" s="61"/>
     </row>
     <row r="856" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="25"/>
-      <c r="E856" s="60"/>
+      <c r="E856" s="61"/>
     </row>
     <row r="857" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="25"/>
-      <c r="E857" s="60"/>
+      <c r="E857" s="61"/>
     </row>
     <row r="858" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="25"/>
-      <c r="E858" s="60"/>
+      <c r="E858" s="61"/>
     </row>
     <row r="859" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="25"/>
-      <c r="E859" s="60"/>
+      <c r="E859" s="61"/>
     </row>
     <row r="860" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="25"/>
-      <c r="E860" s="60"/>
+      <c r="E860" s="61"/>
     </row>
     <row r="861" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="25"/>
-      <c r="E861" s="60"/>
+      <c r="E861" s="61"/>
     </row>
     <row r="862" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="25"/>
-      <c r="E862" s="60"/>
+      <c r="E862" s="61"/>
     </row>
     <row r="863" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="25"/>
-      <c r="E863" s="60"/>
+      <c r="E863" s="61"/>
     </row>
     <row r="864" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="25"/>
-      <c r="E864" s="60"/>
+      <c r="E864" s="61"/>
     </row>
     <row r="865" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="25"/>
-      <c r="E865" s="60"/>
+      <c r="E865" s="61"/>
     </row>
     <row r="866" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="25"/>
-      <c r="E866" s="60"/>
+      <c r="E866" s="61"/>
     </row>
     <row r="867" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="25"/>
-      <c r="E867" s="60"/>
+      <c r="E867" s="61"/>
     </row>
     <row r="868" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="25"/>
-      <c r="E868" s="60"/>
+      <c r="E868" s="61"/>
     </row>
     <row r="869" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="25"/>
-      <c r="E869" s="60"/>
+      <c r="E869" s="61"/>
     </row>
     <row r="870" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="25"/>
-      <c r="E870" s="60"/>
+      <c r="E870" s="61"/>
     </row>
     <row r="871" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="25"/>
-      <c r="E871" s="60"/>
+      <c r="E871" s="61"/>
     </row>
     <row r="872" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="25"/>
-      <c r="E872" s="60"/>
+      <c r="E872" s="61"/>
     </row>
     <row r="873" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="25"/>
-      <c r="E873" s="60"/>
+      <c r="E873" s="61"/>
     </row>
     <row r="874" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="25"/>
-      <c r="E874" s="60"/>
+      <c r="E874" s="61"/>
     </row>
     <row r="875" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="25"/>
-      <c r="E875" s="60"/>
+      <c r="E875" s="61"/>
     </row>
     <row r="876" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="25"/>
-      <c r="E876" s="60"/>
+      <c r="E876" s="61"/>
     </row>
     <row r="877" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="25"/>
-      <c r="E877" s="60"/>
+      <c r="E877" s="61"/>
     </row>
     <row r="878" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="25"/>
-      <c r="E878" s="60"/>
+      <c r="E878" s="61"/>
     </row>
     <row r="879" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="25"/>
-      <c r="E879" s="60"/>
+      <c r="E879" s="61"/>
     </row>
     <row r="880" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="25"/>
-      <c r="E880" s="60"/>
+      <c r="E880" s="61"/>
     </row>
     <row r="881" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="25"/>
-      <c r="E881" s="60"/>
+      <c r="E881" s="61"/>
     </row>
     <row r="882" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="25"/>
-      <c r="E882" s="60"/>
+      <c r="E882" s="61"/>
     </row>
     <row r="883" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="25"/>
-      <c r="E883" s="60"/>
+      <c r="E883" s="61"/>
     </row>
     <row r="884" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="25"/>
-      <c r="E884" s="60"/>
+      <c r="E884" s="61"/>
     </row>
     <row r="885" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="25"/>
-      <c r="E885" s="60"/>
+      <c r="E885" s="61"/>
     </row>
     <row r="886" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="25"/>
-      <c r="E886" s="60"/>
+      <c r="E886" s="61"/>
     </row>
     <row r="887" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="25"/>
-      <c r="E887" s="60"/>
+      <c r="E887" s="61"/>
     </row>
     <row r="888" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="25"/>
-      <c r="E888" s="60"/>
+      <c r="E888" s="61"/>
     </row>
     <row r="889" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="25"/>
-      <c r="E889" s="60"/>
+      <c r="E889" s="61"/>
     </row>
     <row r="890" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="25"/>
-      <c r="E890" s="60"/>
+      <c r="E890" s="61"/>
     </row>
     <row r="891" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="25"/>
-      <c r="E891" s="60"/>
+      <c r="E891" s="61"/>
     </row>
     <row r="892" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="25"/>
-      <c r="E892" s="60"/>
+      <c r="E892" s="61"/>
     </row>
     <row r="893" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="25"/>
-      <c r="E893" s="60"/>
+      <c r="E893" s="61"/>
     </row>
     <row r="894" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="25"/>
-      <c r="E894" s="60"/>
+      <c r="E894" s="61"/>
     </row>
     <row r="895" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="25"/>
-      <c r="E895" s="60"/>
+      <c r="E895" s="61"/>
     </row>
     <row r="896" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="25"/>
-      <c r="E896" s="60"/>
+      <c r="E896" s="61"/>
     </row>
     <row r="897" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="25"/>
-      <c r="E897" s="60"/>
+      <c r="E897" s="61"/>
     </row>
     <row r="898" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="25"/>
-      <c r="E898" s="60"/>
+      <c r="E898" s="61"/>
     </row>
     <row r="899" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="25"/>
-      <c r="E899" s="60"/>
+      <c r="E899" s="61"/>
     </row>
     <row r="900" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="25"/>
-      <c r="E900" s="60"/>
+      <c r="E900" s="61"/>
     </row>
     <row r="901" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="25"/>
-      <c r="E901" s="60"/>
+      <c r="E901" s="61"/>
     </row>
     <row r="902" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="25"/>
-      <c r="E902" s="60"/>
+      <c r="E902" s="61"/>
     </row>
     <row r="903" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="25"/>
-      <c r="E903" s="60"/>
+      <c r="E903" s="61"/>
     </row>
     <row r="904" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="25"/>
-      <c r="E904" s="60"/>
+      <c r="E904" s="61"/>
     </row>
     <row r="905" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="25"/>
-      <c r="E905" s="60"/>
+      <c r="E905" s="61"/>
     </row>
     <row r="906" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="25"/>
-      <c r="E906" s="60"/>
+      <c r="E906" s="61"/>
     </row>
     <row r="907" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="25"/>
-      <c r="E907" s="60"/>
+      <c r="E907" s="61"/>
     </row>
     <row r="908" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="25"/>
-      <c r="E908" s="60"/>
+      <c r="E908" s="61"/>
     </row>
     <row r="909" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="25"/>
-      <c r="E909" s="60"/>
+      <c r="E909" s="61"/>
     </row>
     <row r="910" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="25"/>
-      <c r="E910" s="60"/>
+      <c r="E910" s="61"/>
     </row>
     <row r="911" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="25"/>
-      <c r="E911" s="60"/>
+      <c r="E911" s="61"/>
     </row>
     <row r="912" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="25"/>
-      <c r="E912" s="60"/>
+      <c r="E912" s="61"/>
     </row>
     <row r="913" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="25"/>
-      <c r="E913" s="60"/>
+      <c r="E913" s="61"/>
     </row>
     <row r="914" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="25"/>
-      <c r="E914" s="60"/>
+      <c r="E914" s="61"/>
     </row>
     <row r="915" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="25"/>
-      <c r="E915" s="60"/>
+      <c r="E915" s="61"/>
     </row>
     <row r="916" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="25"/>
-      <c r="E916" s="60"/>
+      <c r="E916" s="61"/>
     </row>
     <row r="917" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="25"/>
-      <c r="E917" s="60"/>
+      <c r="E917" s="61"/>
     </row>
     <row r="918" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="25"/>
-      <c r="E918" s="60"/>
+      <c r="E918" s="61"/>
     </row>
     <row r="919" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="25"/>
-      <c r="E919" s="60"/>
+      <c r="E919" s="61"/>
     </row>
     <row r="920" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="25"/>
-      <c r="E920" s="60"/>
+      <c r="E920" s="61"/>
     </row>
     <row r="921" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="25"/>
-      <c r="E921" s="60"/>
+      <c r="E921" s="61"/>
     </row>
     <row r="922" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="25"/>
-      <c r="E922" s="60"/>
+      <c r="E922" s="61"/>
     </row>
     <row r="923" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="25"/>
-      <c r="E923" s="60"/>
+      <c r="E923" s="61"/>
     </row>
     <row r="924" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="25"/>
-      <c r="E924" s="60"/>
+      <c r="E924" s="61"/>
     </row>
     <row r="925" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="25"/>
-      <c r="E925" s="60"/>
+      <c r="E925" s="61"/>
     </row>
     <row r="926" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="25"/>
-      <c r="E926" s="60"/>
+      <c r="E926" s="61"/>
     </row>
     <row r="927" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="25"/>
-      <c r="E927" s="60"/>
+      <c r="E927" s="61"/>
     </row>
     <row r="928" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="25"/>
-      <c r="E928" s="60"/>
+      <c r="E928" s="61"/>
     </row>
     <row r="929" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="25"/>
-      <c r="E929" s="60"/>
+      <c r="E929" s="61"/>
     </row>
     <row r="930" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="25"/>
-      <c r="E930" s="60"/>
+      <c r="E930" s="61"/>
     </row>
     <row r="931" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="25"/>
-      <c r="E931" s="60"/>
+      <c r="E931" s="61"/>
     </row>
     <row r="932" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="25"/>
-      <c r="E932" s="60"/>
+      <c r="E932" s="61"/>
     </row>
     <row r="933" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="25"/>
-      <c r="E933" s="60"/>
+      <c r="E933" s="61"/>
     </row>
     <row r="934" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="25"/>
-      <c r="E934" s="60"/>
+      <c r="E934" s="61"/>
     </row>
     <row r="935" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="25"/>
-      <c r="E935" s="60"/>
+      <c r="E935" s="61"/>
     </row>
     <row r="936" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="25"/>
-      <c r="E936" s="60"/>
+      <c r="E936" s="61"/>
     </row>
     <row r="937" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="25"/>
-      <c r="E937" s="60"/>
+      <c r="E937" s="61"/>
     </row>
     <row r="938" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="25"/>
-      <c r="E938" s="60"/>
+      <c r="E938" s="61"/>
     </row>
     <row r="939" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="25"/>
-      <c r="E939" s="60"/>
+      <c r="E939" s="61"/>
     </row>
     <row r="940" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="25"/>
-      <c r="E940" s="60"/>
+      <c r="E940" s="61"/>
     </row>
     <row r="941" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="25"/>
-      <c r="E941" s="60"/>
+      <c r="E941" s="61"/>
     </row>
     <row r="942" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="25"/>
-      <c r="E942" s="60"/>
+      <c r="E942" s="61"/>
     </row>
     <row r="943" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="25"/>
-      <c r="E943" s="60"/>
+      <c r="E943" s="61"/>
     </row>
     <row r="944" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="25"/>
-      <c r="E944" s="60"/>
+      <c r="E944" s="61"/>
     </row>
     <row r="945" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="25"/>
-      <c r="E945" s="60"/>
+      <c r="E945" s="61"/>
     </row>
     <row r="946" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="25"/>
-      <c r="E946" s="60"/>
+      <c r="E946" s="61"/>
     </row>
     <row r="947" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="25"/>
-      <c r="E947" s="60"/>
+      <c r="E947" s="61"/>
     </row>
     <row r="948" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="25"/>
-      <c r="E948" s="60"/>
+      <c r="E948" s="61"/>
     </row>
     <row r="949" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="25"/>
-      <c r="E949" s="60"/>
+      <c r="E949" s="61"/>
     </row>
     <row r="950" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="25"/>
-      <c r="E950" s="60"/>
+      <c r="E950" s="61"/>
     </row>
     <row r="951" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="25"/>
-      <c r="E951" s="60"/>
+      <c r="E951" s="61"/>
     </row>
     <row r="952" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="25"/>
-      <c r="E952" s="60"/>
+      <c r="E952" s="61"/>
     </row>
     <row r="953" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="25"/>
-      <c r="E953" s="60"/>
+      <c r="E953" s="61"/>
     </row>
     <row r="954" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="25"/>
-      <c r="E954" s="60"/>
+      <c r="E954" s="61"/>
     </row>
     <row r="955" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="25"/>
-      <c r="E955" s="60"/>
+      <c r="E955" s="61"/>
     </row>
     <row r="956" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="25"/>
-      <c r="E956" s="60"/>
+      <c r="E956" s="61"/>
     </row>
     <row r="957" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="25"/>
-      <c r="E957" s="60"/>
+      <c r="E957" s="61"/>
     </row>
     <row r="958" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="25"/>
-      <c r="E958" s="60"/>
+      <c r="E958" s="61"/>
     </row>
     <row r="959" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="25"/>
-      <c r="E959" s="60"/>
+      <c r="E959" s="61"/>
     </row>
     <row r="960" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="25"/>
-      <c r="E960" s="60"/>
+      <c r="E960" s="61"/>
     </row>
     <row r="961" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="25"/>
-      <c r="E961" s="60"/>
+      <c r="E961" s="61"/>
     </row>
     <row r="962" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="25"/>
-      <c r="E962" s="60"/>
+      <c r="E962" s="61"/>
     </row>
     <row r="963" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="25"/>
-      <c r="E963" s="60"/>
+      <c r="E963" s="61"/>
     </row>
     <row r="964" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="25"/>
-      <c r="E964" s="60"/>
+      <c r="E964" s="61"/>
     </row>
     <row r="965" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="25"/>
-      <c r="E965" s="60"/>
+      <c r="E965" s="61"/>
     </row>
     <row r="966" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="25"/>
-      <c r="E966" s="60"/>
+      <c r="E966" s="61"/>
     </row>
     <row r="967" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="25"/>
-      <c r="E967" s="60"/>
+      <c r="E967" s="61"/>
     </row>
     <row r="968" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="25"/>
-      <c r="E968" s="60"/>
+      <c r="E968" s="61"/>
     </row>
     <row r="969" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="25"/>
-      <c r="E969" s="60"/>
+      <c r="E969" s="61"/>
     </row>
     <row r="970" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="25"/>
-      <c r="E970" s="60"/>
+      <c r="E970" s="61"/>
     </row>
     <row r="971" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="25"/>
-      <c r="E971" s="60"/>
+      <c r="E971" s="61"/>
     </row>
     <row r="972" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="25"/>
-      <c r="E972" s="60"/>
+      <c r="E972" s="61"/>
     </row>
     <row r="973" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="25"/>
-      <c r="E973" s="60"/>
+      <c r="E973" s="61"/>
     </row>
     <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="25"/>
-      <c r="E974" s="60"/>
+      <c r="E974" s="61"/>
     </row>
     <row r="975" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="25"/>
-      <c r="E975" s="60"/>
+      <c r="E975" s="61"/>
     </row>
     <row r="976" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="25"/>
-      <c r="E976" s="60"/>
+      <c r="E976" s="61"/>
     </row>
     <row r="977" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="25"/>
-      <c r="E977" s="60"/>
+      <c r="E977" s="61"/>
     </row>
     <row r="978" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="25"/>
-      <c r="E978" s="60"/>
+      <c r="E978" s="61"/>
     </row>
     <row r="979" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="25"/>
-      <c r="E979" s="60"/>
+      <c r="E979" s="61"/>
     </row>
     <row r="980" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="25"/>
-      <c r="E980" s="60"/>
+      <c r="E980" s="61"/>
     </row>
     <row r="981" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="25"/>
-      <c r="E981" s="60"/>
+      <c r="E981" s="61"/>
     </row>
     <row r="982" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="25"/>
-      <c r="E982" s="60"/>
+      <c r="E982" s="61"/>
     </row>
     <row r="983" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="25"/>
-      <c r="E983" s="60"/>
+      <c r="E983" s="61"/>
     </row>
     <row r="984" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="25"/>
-      <c r="E984" s="60"/>
+      <c r="E984" s="61"/>
     </row>
     <row r="985" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="25"/>
-      <c r="E985" s="60"/>
+      <c r="E985" s="61"/>
     </row>
     <row r="986" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="25"/>
-      <c r="E986" s="60"/>
+      <c r="E986" s="61"/>
     </row>
     <row r="987" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="25"/>
-      <c r="E987" s="60"/>
+      <c r="E987" s="61"/>
     </row>
     <row r="988" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="25"/>
-      <c r="E988" s="60"/>
+      <c r="E988" s="61"/>
     </row>
     <row r="989" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="25"/>
-      <c r="E989" s="60"/>
+      <c r="E989" s="61"/>
     </row>
     <row r="990" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="25"/>
-      <c r="E990" s="60"/>
+      <c r="E990" s="61"/>
     </row>
     <row r="991" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="25"/>
-      <c r="E991" s="60"/>
+      <c r="E991" s="61"/>
     </row>
     <row r="992" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="25"/>
-      <c r="E992" s="60"/>
+      <c r="E992" s="61"/>
     </row>
     <row r="993" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="25"/>
-      <c r="E993" s="60"/>
+      <c r="E993" s="61"/>
     </row>
     <row r="994" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="25"/>
-      <c r="E994" s="60"/>
+      <c r="E994" s="61"/>
     </row>
     <row r="995" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="25"/>
-      <c r="E995" s="60"/>
+      <c r="E995" s="61"/>
     </row>
     <row r="996" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="25"/>
-      <c r="E996" s="60"/>
+      <c r="E996" s="61"/>
     </row>
     <row r="997" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="25"/>
-      <c r="E997" s="60"/>
+      <c r="E997" s="61"/>
     </row>
     <row r="998" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="25"/>
-      <c r="E998" s="60"/>
+      <c r="E998" s="61"/>
     </row>
     <row r="999" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="25"/>
-      <c r="E999" s="60"/>
+      <c r="E999" s="61"/>
     </row>
     <row r="1000" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="25"/>
-      <c r="E1000" s="60"/>
+      <c r="E1000" s="61"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1">
@@ -18451,453 +18451,255 @@
   <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("UNIQUE(
-  FILTER(
-    {Decisions!A2:A1000; Softwares!A2:A1000; Hardwares!A2:A1000},
-    {Decisions!A2:A1000; Softwares!A2:A1000; Hardwares!A2:A1000} &lt;&gt; """"
-  )
-)"),1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),2)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),3)</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),4)</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),5)</f>
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),6)</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),7)</f>
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),8)</f>
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),9)</f>
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),10)</f>
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),11)</f>
         <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),12)</f>
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),13)</f>
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),14)</f>
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),15)</f>
         <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),16)</f>
         <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),17)</f>
         <v>17</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),18)</f>
         <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),19)</f>
         <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),20)</f>
         <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),21)</f>
         <v>21</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),22)</f>
         <v>22</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),23)</f>
         <v>23</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),24)</f>
         <v>24</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),25)</f>
         <v>25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),26)</f>
         <v>26</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),27)</f>
         <v>27</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),28)</f>
         <v>28</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),29)</f>
         <v>29</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),30)</f>
         <v>30</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),31)</f>
         <v>31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),32)</f>
         <v>32</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),33)</f>
         <v>33</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),34)</f>
         <v>34</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),35)</f>
         <v>35</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),36)</f>
         <v>36</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),37)</f>
         <v>37</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="62" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),38)</f>
         <v>38</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),101)</f>
-        <v>101</v>
+      <c r="A40" s="62" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),102)</f>
-        <v>102</v>
+      <c r="A41" s="62" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),103)</f>
-        <v>103</v>
+      <c r="A42" s="62" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),104)</f>
-        <v>104</v>
+      <c r="A43" s="62" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),105)</f>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),106)</f>
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),107)</f>
-        <v>107</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),108)</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),109)</f>
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),110)</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),111)</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),112)</f>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),135)</f>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),201)</f>
-        <v>201</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),202)</f>
-        <v>202</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),203)</f>
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),204)</f>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),205)</f>
-        <v>205</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),206)</f>
-        <v>206</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),207)</f>
-        <v>207</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),208)</f>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),209)</f>
-        <v>209</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),210)</f>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),211)</f>
-        <v>211</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),212)</f>
-        <v>212</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),213)</f>
-        <v>213</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),214)</f>
-        <v>214</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),215)</f>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),216)</f>
-        <v>216</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),217)</f>
-        <v>217</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),218)</f>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),219)</f>
-        <v>219</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),220)</f>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),221)</f>
-        <v>221</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="26" t="n">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),222)</f>
-        <v>222</v>
-      </c>
-    </row>
+      <c r="A44" s="62" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
